--- a/public/building01.xlsx
+++ b/public/building01.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>Flr</t>
   </si>
@@ -48,7 +48,7 @@
     <t>1BHK</t>
   </si>
   <si>
-    <t>john Doe</t>
+    <t>Mukesh</t>
   </si>
   <si>
     <t>yes</t>
@@ -60,6 +60,9 @@
     <t>no</t>
   </si>
   <si>
+    <t>Nilesh</t>
+  </si>
+  <si>
     <t>2nd</t>
   </si>
   <si>
@@ -67,9 +70,6 @@
   </si>
   <si>
     <t>3BHK</t>
-  </si>
-  <si>
-    <t>3-john Doe</t>
   </si>
 </sst>
 </file>
@@ -116,10 +116,10 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -388,7 +388,7 @@
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1">
@@ -414,9 +414,7 @@
       <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="D3" s="1"/>
       <c r="E3" s="1">
         <v>242.0</v>
       </c>
@@ -440,8 +438,8 @@
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E4" s="1">
         <v>432.0</v>
@@ -452,7 +450,7 @@
       <c r="G4" s="1">
         <v>632.0</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -463,12 +461,10 @@
       <c r="B5" s="1">
         <v>104.0</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="D5" s="1"/>
       <c r="E5" s="1">
         <v>334.0</v>
       </c>
@@ -492,9 +488,7 @@
       <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1">
         <v>367.0</v>
       </c>
@@ -518,9 +512,7 @@
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="D7" s="1"/>
       <c r="E7" s="7">
         <v>367.0</v>
       </c>
@@ -544,9 +536,7 @@
       <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="D8" s="1"/>
       <c r="E8" s="7">
         <v>367.0</v>
       </c>
@@ -570,9 +560,7 @@
       <c r="C9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="D9" s="1"/>
       <c r="E9" s="7">
         <v>367.0</v>
       </c>
@@ -596,9 +584,7 @@
       <c r="C10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="D10" s="1"/>
       <c r="E10" s="7">
         <v>367.0</v>
       </c>
@@ -614,17 +600,15 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="4">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3">
         <v>201.0</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="D11" s="1"/>
       <c r="E11" s="1">
         <v>523.0</v>
       </c>
@@ -640,21 +624,19 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3">
         <v>202.0</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="D12" s="1"/>
       <c r="E12" s="1">
         <v>123.0</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>832.0</v>
       </c>
       <c r="G12" s="1">
@@ -666,17 +648,15 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3">
         <v>203.0</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="D13" s="1"/>
       <c r="E13" s="1">
         <v>214.0</v>
       </c>
@@ -692,17 +672,15 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="9">
         <v>301.0</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="D14" s="1"/>
       <c r="E14" s="1">
         <v>523.0</v>
       </c>

--- a/public/building01.xlsx
+++ b/public/building01.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="26">
   <si>
     <t>Flr</t>
   </si>
   <si>
-    <t>Flat No.</t>
+    <t>FlatNo</t>
   </si>
   <si>
     <t>Type</t>
@@ -42,7 +42,10 @@
     <t>Sold</t>
   </si>
   <si>
-    <t>1st</t>
+    <t>height</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>1BHK</t>
@@ -54,19 +57,43 @@
     <t>yes</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>2BHK</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Nilesh</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>no</t>
   </si>
   <si>
-    <t>Nilesh</t>
+    <t>8</t>
   </si>
   <si>
-    <t>2nd</t>
+    <t>9</t>
   </si>
   <si>
     <t>Ramesh</t>
+  </si>
+  <si>
+    <t>Shtish</t>
   </si>
 </sst>
 </file>
@@ -104,25 +131,29 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -130,6 +161,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -346,3434 +381,5150 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3.75"/>
-    <col customWidth="1" min="2" max="2" width="6.88"/>
-    <col customWidth="1" min="3" max="3" width="5.38"/>
-    <col customWidth="1" min="4" max="4" width="6.88"/>
-    <col customWidth="1" min="5" max="5" width="6.0"/>
-    <col customWidth="1" min="6" max="6" width="6.5"/>
-    <col customWidth="1" min="7" max="7" width="10.0"/>
-    <col customWidth="1" min="8" max="8" width="4.38"/>
+    <col customWidth="1" min="1" max="26" width="8.13"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3">
         <v>101.0</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1">
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3">
         <v>367.0</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="3">
         <v>53.0</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="3">
         <v>429.0</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>11</v>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="5">
+        <v>10.0</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3">
         <v>102.0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <v>242.0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>53.0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>290.0</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1">
+      <c r="I3" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3">
+        <v>103.0</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3">
+        <v>432.0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>74.0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>632.0</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3">
+        <v>104.0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3">
+        <v>334.0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>80.0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>124.0</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="3">
+        <v>105.0</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3">
+        <v>367.0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="G6" s="3">
         <v>242.0</v>
       </c>
-      <c r="F3" s="1">
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7">
+        <v>106.0</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="7">
+        <v>107.0</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F8" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="7">
+        <v>108.0</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F9" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="7">
+        <v>109.0</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2">
+        <v>201.0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="3">
+        <v>367.0</v>
+      </c>
+      <c r="F11" s="3">
         <v>53.0</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G11" s="3">
+        <v>429.0</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <v>202.0</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>242.0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>53.0</v>
+      </c>
+      <c r="G12" s="3">
         <v>290.0</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1">
-        <v>103.0</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="B13" s="2">
+        <v>203.0</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="1">
+      <c r="D13" s="2"/>
+      <c r="E13" s="3">
         <v>432.0</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F13" s="3">
         <v>74.0</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G13" s="3">
         <v>632.0</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
-        <v>104.0</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1">
+      <c r="H13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>204.0</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3">
         <v>334.0</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F14" s="3">
         <v>80.0</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G14" s="3">
         <v>124.0</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1">
-        <v>105.0</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
+      <c r="B15" s="2">
+        <v>205.0</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3">
         <v>367.0</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F15" s="3">
         <v>26.0</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G15" s="3">
         <v>242.0</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6">
-        <v>106.0</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="7">
+      <c r="B16" s="2">
+        <v>206.0</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="9">
         <v>367.0</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F16" s="9">
         <v>26.0</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G16" s="9">
         <v>242.0</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="6">
-        <v>107.0</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="7">
+      <c r="B17" s="2">
+        <v>207.0</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="9">
         <v>367.0</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F17" s="9">
         <v>26.0</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G17" s="9">
         <v>242.0</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <v>108.0</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="7">
+      <c r="B18" s="2">
+        <v>208.0</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="9">
         <v>367.0</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F18" s="9">
         <v>26.0</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G18" s="9">
         <v>242.0</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6">
-        <v>109.0</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="7">
+      <c r="B19" s="2">
+        <v>209.0</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="9">
         <v>367.0</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F19" s="9">
         <v>26.0</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G19" s="9">
         <v>242.0</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
+      <c r="H19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3">
-        <v>201.0</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="B20" s="2">
+        <v>301.0</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="3">
         <v>367.0</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F20" s="3">
         <v>53.0</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G20" s="3">
         <v>429.0</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="1" t="s">
+      <c r="H20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3">
-        <v>202.0</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1">
+      <c r="B21" s="2">
+        <v>302.0</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
         <v>242.0</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F21" s="3">
         <v>53.0</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G21" s="3">
         <v>290.0</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1" t="s">
+      <c r="H21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3">
-        <v>203.0</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="1">
+      <c r="B22" s="2">
+        <v>303.0</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3">
         <v>432.0</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F22" s="3">
         <v>74.0</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G22" s="3">
         <v>632.0</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
+      <c r="H22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="3">
-        <v>204.0</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1">
+      <c r="B23" s="2">
+        <v>304.0</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3">
         <v>334.0</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F23" s="3">
         <v>80.0</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G23" s="3">
         <v>124.0</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="s">
+      <c r="H23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="3">
-        <v>205.0</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1">
+      <c r="B24" s="2">
+        <v>305.0</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3">
         <v>367.0</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F24" s="3">
         <v>26.0</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G24" s="3">
         <v>242.0</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="1" t="s">
+      <c r="H24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6">
-        <v>206.0</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="7">
+      <c r="B25" s="2">
+        <v>306.0</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="9">
         <v>367.0</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F25" s="9">
         <v>26.0</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G25" s="9">
         <v>242.0</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1" t="s">
+      <c r="H25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="6">
-        <v>207.0</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="7">
+      <c r="B26" s="2">
+        <v>307.0</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="9">
         <v>367.0</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F26" s="9">
         <v>26.0</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G26" s="9">
         <v>242.0</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="1" t="s">
+      <c r="H26" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="6">
-        <v>208.0</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="7">
+      <c r="B27" s="2">
+        <v>308.0</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="9">
         <v>367.0</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F27" s="9">
         <v>26.0</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G27" s="9">
         <v>242.0</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="1" t="s">
+      <c r="H27" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="5">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="6">
-        <v>209.0</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="7">
+      <c r="B28" s="2">
+        <v>309.0</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="9">
         <v>367.0</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F28" s="9">
         <v>26.0</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G28" s="9">
         <v>242.0</v>
       </c>
-      <c r="H19" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="H28" s="9"/>
+      <c r="H28" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="H29" s="9"/>
+      <c r="A29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="5">
+        <v>401.0</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3">
+        <v>367.0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>242.0</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="H30" s="9"/>
+      <c r="A30" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="5">
+        <v>402.0</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="H31" s="9"/>
+      <c r="A31" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="5">
+        <v>403.0</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F31" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="H32" s="9"/>
+      <c r="A32" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="5">
+        <v>404.0</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="H33" s="9"/>
+      <c r="A33" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="5">
+        <v>405.0</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F33" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="H34" s="9"/>
+      <c r="A34" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="5">
+        <v>406.0</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="3">
+        <v>367.0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>53.0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>429.0</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="H35" s="9"/>
+      <c r="A35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="5">
+        <v>407.0</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="3">
+        <v>242.0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>53.0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>290.0</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="H36" s="9"/>
+      <c r="A36" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="5">
+        <v>408.0</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="3">
+        <v>432.0</v>
+      </c>
+      <c r="F36" s="3">
+        <v>74.0</v>
+      </c>
+      <c r="G36" s="3">
+        <v>632.0</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="H37" s="9"/>
+      <c r="A37" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="5">
+        <v>409.0</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3">
+        <v>334.0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>80.0</v>
+      </c>
+      <c r="G37" s="3">
+        <v>124.0</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="H38" s="9"/>
+      <c r="A38" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="5">
+        <v>501.0</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3">
+        <v>367.0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="G38" s="3">
+        <v>242.0</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="H39" s="9"/>
+      <c r="A39" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="5">
+        <v>502.0</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3">
+        <v>367.0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>242.0</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="H40" s="9"/>
+      <c r="A40" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="5">
+        <v>503.0</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F40" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="H41" s="9"/>
+      <c r="A41" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="5">
+        <v>504.0</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F41" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G41" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="H42" s="9"/>
+      <c r="A42" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="5">
+        <v>505.0</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F42" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G42" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="H43" s="9"/>
+      <c r="A43" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="5">
+        <v>506.0</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="9">
+        <v>367.0</v>
+      </c>
+      <c r="F43" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G43" s="9">
+        <v>242.0</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="H44" s="9"/>
+      <c r="A44" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="5">
+        <v>507.0</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="3">
+        <v>367.0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>53.0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>429.0</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="H45" s="9"/>
+      <c r="A45" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="5">
+        <v>508.0</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="3">
+        <v>242.0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>53.0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>290.0</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="H46" s="9"/>
+      <c r="A46" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="5">
+        <v>509.0</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="3">
+        <v>432.0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>74.0</v>
+      </c>
+      <c r="G46" s="3">
+        <v>632.0</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="H47" s="9"/>
+      <c r="A47" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="5">
+        <v>601.0</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3">
+        <v>334.0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>80.0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>124.0</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="H48" s="9"/>
+      <c r="A48" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="5">
+        <v>602.0</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3">
+        <v>367.0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>242.0</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="5">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="H49" s="9"/>
+      <c r="A49" s="12"/>
+      <c r="H49" s="13"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="H50" s="9"/>
+      <c r="A50" s="12"/>
+      <c r="H50" s="13"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="H51" s="9"/>
+      <c r="A51" s="12"/>
+      <c r="H51" s="13"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="H52" s="9"/>
+      <c r="A52" s="12"/>
+      <c r="H52" s="13"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="H53" s="9"/>
+      <c r="A53" s="12"/>
+      <c r="H53" s="13"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="H54" s="9"/>
+      <c r="A54" s="12"/>
+      <c r="H54" s="13"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="H55" s="9"/>
+      <c r="A55" s="12"/>
+      <c r="H55" s="13"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="H56" s="9"/>
+      <c r="A56" s="12"/>
+      <c r="H56" s="13"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="H57" s="9"/>
+      <c r="A57" s="12"/>
+      <c r="H57" s="13"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="H58" s="9"/>
+      <c r="A58" s="12"/>
+      <c r="H58" s="13"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="H59" s="9"/>
+      <c r="A59" s="12"/>
+      <c r="H59" s="13"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="H60" s="9"/>
+      <c r="A60" s="12"/>
+      <c r="H60" s="13"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="H61" s="9"/>
+      <c r="A61" s="12"/>
+      <c r="H61" s="13"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="H62" s="9"/>
+      <c r="A62" s="12"/>
+      <c r="H62" s="13"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="H63" s="9"/>
+      <c r="A63" s="12"/>
+      <c r="H63" s="13"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="H64" s="9"/>
+      <c r="A64" s="12"/>
+      <c r="H64" s="13"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="H65" s="9"/>
+      <c r="A65" s="12"/>
+      <c r="H65" s="13"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="H66" s="9"/>
+      <c r="A66" s="12"/>
+      <c r="H66" s="13"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="H67" s="9"/>
+      <c r="A67" s="12"/>
+      <c r="H67" s="13"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="H68" s="9"/>
+      <c r="A68" s="12"/>
+      <c r="H68" s="13"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="H69" s="9"/>
+      <c r="A69" s="12"/>
+      <c r="H69" s="13"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="H70" s="9"/>
+      <c r="A70" s="12"/>
+      <c r="H70" s="13"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="H71" s="9"/>
+      <c r="A71" s="12"/>
+      <c r="H71" s="13"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="H72" s="9"/>
+      <c r="A72" s="12"/>
+      <c r="H72" s="13"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="H73" s="9"/>
+      <c r="A73" s="12"/>
+      <c r="H73" s="13"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="H74" s="9"/>
+      <c r="A74" s="12"/>
+      <c r="H74" s="13"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="H75" s="9"/>
+      <c r="A75" s="12"/>
+      <c r="H75" s="13"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="H76" s="9"/>
+      <c r="A76" s="12"/>
+      <c r="H76" s="13"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="H77" s="9"/>
+      <c r="A77" s="12"/>
+      <c r="H77" s="13"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="H78" s="9"/>
+      <c r="A78" s="12"/>
+      <c r="H78" s="13"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="H79" s="9"/>
+      <c r="A79" s="12"/>
+      <c r="H79" s="13"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="H80" s="9"/>
+      <c r="A80" s="12"/>
+      <c r="H80" s="13"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="H81" s="9"/>
+      <c r="A81" s="12"/>
+      <c r="H81" s="13"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="H82" s="9"/>
+      <c r="A82" s="12"/>
+      <c r="H82" s="13"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="H83" s="9"/>
+      <c r="A83" s="12"/>
+      <c r="H83" s="13"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="H84" s="9"/>
+      <c r="A84" s="12"/>
+      <c r="H84" s="13"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="H85" s="9"/>
+      <c r="A85" s="12"/>
+      <c r="H85" s="13"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="H86" s="9"/>
+      <c r="A86" s="12"/>
+      <c r="H86" s="13"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="H87" s="9"/>
+      <c r="A87" s="12"/>
+      <c r="H87" s="13"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="H88" s="9"/>
+      <c r="A88" s="12"/>
+      <c r="H88" s="13"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="H89" s="9"/>
+      <c r="A89" s="12"/>
+      <c r="H89" s="13"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="H90" s="9"/>
+      <c r="A90" s="12"/>
+      <c r="H90" s="13"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="H91" s="9"/>
+      <c r="A91" s="12"/>
+      <c r="H91" s="13"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="H92" s="9"/>
+      <c r="A92" s="12"/>
+      <c r="H92" s="13"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="H93" s="9"/>
+      <c r="A93" s="12"/>
+      <c r="H93" s="13"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="H94" s="9"/>
+      <c r="A94" s="12"/>
+      <c r="H94" s="13"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="H95" s="9"/>
+      <c r="A95" s="12"/>
+      <c r="H95" s="13"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="H96" s="9"/>
+      <c r="A96" s="12"/>
+      <c r="H96" s="13"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="H97" s="9"/>
+      <c r="A97" s="12"/>
+      <c r="H97" s="13"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="H98" s="9"/>
+      <c r="A98" s="12"/>
+      <c r="H98" s="13"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="H99" s="9"/>
+      <c r="A99" s="12"/>
+      <c r="H99" s="13"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="H100" s="9"/>
+      <c r="A100" s="12"/>
+      <c r="H100" s="13"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="H101" s="9"/>
+      <c r="A101" s="12"/>
+      <c r="H101" s="13"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="H102" s="9"/>
+      <c r="A102" s="12"/>
+      <c r="H102" s="13"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="H103" s="9"/>
+      <c r="A103" s="12"/>
+      <c r="H103" s="13"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="H104" s="9"/>
+      <c r="A104" s="12"/>
+      <c r="H104" s="13"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="H105" s="9"/>
+      <c r="A105" s="12"/>
+      <c r="H105" s="13"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="H106" s="9"/>
+      <c r="A106" s="12"/>
+      <c r="H106" s="13"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="H107" s="9"/>
+      <c r="A107" s="12"/>
+      <c r="H107" s="13"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="H108" s="9"/>
+      <c r="A108" s="12"/>
+      <c r="H108" s="13"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="H109" s="9"/>
+      <c r="A109" s="12"/>
+      <c r="H109" s="13"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="H110" s="9"/>
+      <c r="A110" s="12"/>
+      <c r="H110" s="13"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="H111" s="9"/>
+      <c r="A111" s="12"/>
+      <c r="H111" s="13"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="H112" s="9"/>
+      <c r="A112" s="12"/>
+      <c r="H112" s="13"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="H113" s="9"/>
+      <c r="A113" s="12"/>
+      <c r="H113" s="13"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="H114" s="9"/>
+      <c r="A114" s="12"/>
+      <c r="H114" s="13"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="H115" s="9"/>
+      <c r="A115" s="12"/>
+      <c r="H115" s="13"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="H116" s="9"/>
+      <c r="A116" s="12"/>
+      <c r="H116" s="13"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="H117" s="9"/>
+      <c r="A117" s="12"/>
+      <c r="H117" s="13"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="H118" s="9"/>
+      <c r="A118" s="12"/>
+      <c r="H118" s="13"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="H119" s="9"/>
+      <c r="A119" s="12"/>
+      <c r="H119" s="13"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="H120" s="9"/>
+      <c r="A120" s="12"/>
+      <c r="H120" s="13"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="H121" s="9"/>
+      <c r="A121" s="12"/>
+      <c r="H121" s="13"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="H122" s="9"/>
+      <c r="A122" s="12"/>
+      <c r="H122" s="13"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="H123" s="9"/>
+      <c r="A123" s="12"/>
+      <c r="H123" s="13"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="H124" s="9"/>
+      <c r="A124" s="12"/>
+      <c r="H124" s="13"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="H125" s="9"/>
+      <c r="A125" s="12"/>
+      <c r="H125" s="13"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="H126" s="9"/>
+      <c r="A126" s="12"/>
+      <c r="H126" s="13"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="H127" s="9"/>
+      <c r="A127" s="12"/>
+      <c r="H127" s="13"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="H128" s="9"/>
+      <c r="A128" s="12"/>
+      <c r="H128" s="13"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="H129" s="9"/>
+      <c r="A129" s="12"/>
+      <c r="H129" s="13"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="H130" s="9"/>
+      <c r="A130" s="12"/>
+      <c r="H130" s="13"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="H131" s="9"/>
+      <c r="A131" s="12"/>
+      <c r="H131" s="13"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="H132" s="9"/>
+      <c r="A132" s="12"/>
+      <c r="H132" s="13"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="H133" s="9"/>
+      <c r="A133" s="12"/>
+      <c r="H133" s="13"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="H134" s="9"/>
+      <c r="A134" s="12"/>
+      <c r="H134" s="13"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="H135" s="9"/>
+      <c r="A135" s="12"/>
+      <c r="H135" s="13"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="H136" s="9"/>
+      <c r="A136" s="12"/>
+      <c r="H136" s="13"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="H137" s="9"/>
+      <c r="A137" s="12"/>
+      <c r="H137" s="13"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="H138" s="9"/>
+      <c r="A138" s="12"/>
+      <c r="H138" s="13"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="H139" s="9"/>
+      <c r="A139" s="12"/>
+      <c r="H139" s="13"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="H140" s="9"/>
+      <c r="A140" s="12"/>
+      <c r="H140" s="13"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="H141" s="9"/>
+      <c r="A141" s="12"/>
+      <c r="H141" s="13"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="H142" s="9"/>
+      <c r="A142" s="12"/>
+      <c r="H142" s="13"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="H143" s="9"/>
+      <c r="A143" s="12"/>
+      <c r="H143" s="13"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="H144" s="9"/>
+      <c r="A144" s="12"/>
+      <c r="H144" s="13"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="H145" s="9"/>
+      <c r="A145" s="12"/>
+      <c r="H145" s="13"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="H146" s="9"/>
+      <c r="A146" s="12"/>
+      <c r="H146" s="13"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="H147" s="9"/>
+      <c r="A147" s="12"/>
+      <c r="H147" s="13"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="H148" s="9"/>
+      <c r="A148" s="12"/>
+      <c r="H148" s="13"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="H149" s="9"/>
+      <c r="A149" s="12"/>
+      <c r="H149" s="13"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="H150" s="9"/>
+      <c r="A150" s="12"/>
+      <c r="H150" s="13"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="H151" s="9"/>
+      <c r="A151" s="12"/>
+      <c r="H151" s="13"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="H152" s="9"/>
+      <c r="A152" s="12"/>
+      <c r="H152" s="13"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="H153" s="9"/>
+      <c r="A153" s="12"/>
+      <c r="H153" s="13"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="H154" s="9"/>
+      <c r="A154" s="12"/>
+      <c r="H154" s="13"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="H155" s="9"/>
+      <c r="A155" s="12"/>
+      <c r="H155" s="13"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="H156" s="9"/>
+      <c r="A156" s="12"/>
+      <c r="H156" s="13"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="H157" s="9"/>
+      <c r="A157" s="12"/>
+      <c r="H157" s="13"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="H158" s="9"/>
+      <c r="A158" s="12"/>
+      <c r="H158" s="13"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="H159" s="9"/>
+      <c r="A159" s="12"/>
+      <c r="H159" s="13"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="H160" s="9"/>
+      <c r="A160" s="12"/>
+      <c r="H160" s="13"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="H161" s="9"/>
+      <c r="A161" s="12"/>
+      <c r="H161" s="13"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="H162" s="9"/>
+      <c r="A162" s="12"/>
+      <c r="H162" s="13"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="H163" s="9"/>
+      <c r="A163" s="12"/>
+      <c r="H163" s="13"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="H164" s="9"/>
+      <c r="A164" s="12"/>
+      <c r="H164" s="13"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="H165" s="9"/>
+      <c r="A165" s="12"/>
+      <c r="H165" s="13"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="H166" s="9"/>
+      <c r="A166" s="12"/>
+      <c r="H166" s="13"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="H167" s="9"/>
+      <c r="A167" s="12"/>
+      <c r="H167" s="13"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="H168" s="9"/>
+      <c r="A168" s="12"/>
+      <c r="H168" s="13"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="H169" s="9"/>
+      <c r="A169" s="12"/>
+      <c r="H169" s="13"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="H170" s="9"/>
+      <c r="A170" s="12"/>
+      <c r="H170" s="13"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="H171" s="9"/>
+      <c r="A171" s="12"/>
+      <c r="H171" s="13"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="H172" s="9"/>
+      <c r="A172" s="12"/>
+      <c r="H172" s="13"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="H173" s="9"/>
+      <c r="A173" s="12"/>
+      <c r="H173" s="13"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="H174" s="9"/>
+      <c r="A174" s="12"/>
+      <c r="H174" s="13"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="H175" s="9"/>
+      <c r="A175" s="12"/>
+      <c r="H175" s="13"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="H176" s="9"/>
+      <c r="A176" s="12"/>
+      <c r="H176" s="13"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="H177" s="9"/>
+      <c r="A177" s="12"/>
+      <c r="H177" s="13"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="H178" s="9"/>
+      <c r="A178" s="12"/>
+      <c r="H178" s="13"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="H179" s="9"/>
+      <c r="A179" s="12"/>
+      <c r="H179" s="13"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="H180" s="9"/>
+      <c r="A180" s="12"/>
+      <c r="H180" s="13"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="H181" s="9"/>
+      <c r="A181" s="12"/>
+      <c r="H181" s="13"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="H182" s="9"/>
+      <c r="A182" s="12"/>
+      <c r="H182" s="13"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="H183" s="9"/>
+      <c r="A183" s="12"/>
+      <c r="H183" s="13"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="H184" s="9"/>
+      <c r="A184" s="12"/>
+      <c r="H184" s="13"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="H185" s="9"/>
+      <c r="A185" s="12"/>
+      <c r="H185" s="13"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="H186" s="9"/>
+      <c r="A186" s="12"/>
+      <c r="H186" s="13"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="H187" s="9"/>
+      <c r="A187" s="12"/>
+      <c r="H187" s="13"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="H188" s="9"/>
+      <c r="A188" s="12"/>
+      <c r="H188" s="13"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="H189" s="9"/>
+      <c r="A189" s="12"/>
+      <c r="H189" s="13"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="H190" s="9"/>
+      <c r="A190" s="12"/>
+      <c r="H190" s="13"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="H191" s="9"/>
+      <c r="A191" s="12"/>
+      <c r="H191" s="13"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="H192" s="9"/>
+      <c r="A192" s="12"/>
+      <c r="H192" s="13"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="H193" s="9"/>
+      <c r="A193" s="12"/>
+      <c r="H193" s="13"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="H194" s="9"/>
+      <c r="A194" s="12"/>
+      <c r="H194" s="13"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="H195" s="9"/>
+      <c r="A195" s="12"/>
+      <c r="H195" s="13"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="H196" s="9"/>
+      <c r="A196" s="12"/>
+      <c r="H196" s="13"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="H197" s="9"/>
+      <c r="A197" s="12"/>
+      <c r="H197" s="13"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="H198" s="9"/>
+      <c r="A198" s="12"/>
+      <c r="H198" s="13"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="H199" s="9"/>
+      <c r="A199" s="12"/>
+      <c r="H199" s="13"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="H200" s="9"/>
+      <c r="A200" s="12"/>
+      <c r="H200" s="13"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="H201" s="9"/>
+      <c r="A201" s="12"/>
+      <c r="H201" s="13"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="H202" s="9"/>
+      <c r="A202" s="12"/>
+      <c r="H202" s="13"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="H203" s="9"/>
+      <c r="A203" s="12"/>
+      <c r="H203" s="13"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="H204" s="9"/>
+      <c r="A204" s="12"/>
+      <c r="H204" s="13"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="H205" s="9"/>
+      <c r="A205" s="12"/>
+      <c r="H205" s="13"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="H206" s="9"/>
+      <c r="A206" s="12"/>
+      <c r="H206" s="13"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="H207" s="9"/>
+      <c r="A207" s="12"/>
+      <c r="H207" s="13"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="H208" s="9"/>
+      <c r="A208" s="12"/>
+      <c r="H208" s="13"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="H209" s="9"/>
+      <c r="A209" s="12"/>
+      <c r="H209" s="13"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="H210" s="9"/>
+      <c r="A210" s="12"/>
+      <c r="H210" s="13"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="H211" s="9"/>
+      <c r="A211" s="12"/>
+      <c r="H211" s="13"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="H212" s="9"/>
+      <c r="A212" s="12"/>
+      <c r="H212" s="13"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="H213" s="9"/>
+      <c r="A213" s="12"/>
+      <c r="H213" s="13"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="H214" s="9"/>
+      <c r="A214" s="12"/>
+      <c r="H214" s="13"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="H215" s="9"/>
+      <c r="A215" s="12"/>
+      <c r="H215" s="13"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="H216" s="9"/>
+      <c r="A216" s="12"/>
+      <c r="H216" s="13"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="H217" s="9"/>
+      <c r="A217" s="12"/>
+      <c r="H217" s="13"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="H218" s="9"/>
+      <c r="A218" s="12"/>
+      <c r="H218" s="13"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="H219" s="9"/>
+      <c r="A219" s="12"/>
+      <c r="H219" s="13"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="H220" s="9"/>
+      <c r="A220" s="12"/>
+      <c r="H220" s="13"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="H221" s="9"/>
+      <c r="A221" s="12"/>
+      <c r="H221" s="13"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="H222" s="9"/>
+      <c r="A222" s="12"/>
+      <c r="H222" s="13"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="H223" s="9"/>
+      <c r="A223" s="12"/>
+      <c r="H223" s="13"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="H224" s="9"/>
+      <c r="A224" s="12"/>
+      <c r="H224" s="13"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="H225" s="9"/>
+      <c r="A225" s="12"/>
+      <c r="H225" s="13"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="H226" s="9"/>
+      <c r="A226" s="12"/>
+      <c r="H226" s="13"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="H227" s="9"/>
+      <c r="A227" s="12"/>
+      <c r="H227" s="13"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="H228" s="9"/>
+      <c r="A228" s="12"/>
+      <c r="H228" s="13"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="H229" s="9"/>
+      <c r="A229" s="12"/>
+      <c r="H229" s="13"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="H230" s="9"/>
+      <c r="A230" s="12"/>
+      <c r="H230" s="13"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="H231" s="9"/>
+      <c r="A231" s="12"/>
+      <c r="H231" s="13"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="H232" s="9"/>
+      <c r="A232" s="12"/>
+      <c r="H232" s="13"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="H233" s="9"/>
+      <c r="A233" s="12"/>
+      <c r="H233" s="13"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="H234" s="9"/>
+      <c r="A234" s="12"/>
+      <c r="H234" s="13"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="H235" s="9"/>
+      <c r="A235" s="12"/>
+      <c r="H235" s="13"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="H236" s="9"/>
+      <c r="A236" s="12"/>
+      <c r="H236" s="13"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="H237" s="9"/>
+      <c r="A237" s="12"/>
+      <c r="H237" s="13"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="H238" s="9"/>
+      <c r="A238" s="12"/>
+      <c r="H238" s="13"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="H239" s="9"/>
+      <c r="A239" s="12"/>
+      <c r="H239" s="13"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="H240" s="9"/>
+      <c r="A240" s="12"/>
+      <c r="H240" s="13"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="H241" s="9"/>
+      <c r="A241" s="12"/>
+      <c r="H241" s="13"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="H242" s="9"/>
+      <c r="A242" s="12"/>
+      <c r="H242" s="13"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="H243" s="9"/>
+      <c r="A243" s="12"/>
+      <c r="H243" s="13"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="H244" s="9"/>
+      <c r="A244" s="12"/>
+      <c r="H244" s="13"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="H245" s="9"/>
+      <c r="A245" s="12"/>
+      <c r="H245" s="13"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="H246" s="9"/>
+      <c r="A246" s="12"/>
+      <c r="H246" s="13"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="H247" s="9"/>
+      <c r="A247" s="12"/>
+      <c r="H247" s="13"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="H248" s="9"/>
+      <c r="A248" s="12"/>
+      <c r="H248" s="13"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="H249" s="9"/>
+      <c r="A249" s="12"/>
+      <c r="H249" s="13"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="H250" s="9"/>
+      <c r="A250" s="12"/>
+      <c r="H250" s="13"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="H251" s="9"/>
+      <c r="A251" s="12"/>
+      <c r="H251" s="13"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="H252" s="9"/>
+      <c r="A252" s="12"/>
+      <c r="H252" s="13"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="H253" s="9"/>
+      <c r="A253" s="12"/>
+      <c r="H253" s="13"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="H254" s="9"/>
+      <c r="A254" s="12"/>
+      <c r="H254" s="13"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="H255" s="9"/>
+      <c r="A255" s="12"/>
+      <c r="H255" s="13"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="H256" s="9"/>
+      <c r="A256" s="12"/>
+      <c r="H256" s="13"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="H257" s="9"/>
+      <c r="A257" s="12"/>
+      <c r="H257" s="13"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="H258" s="9"/>
+      <c r="A258" s="12"/>
+      <c r="H258" s="13"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="H259" s="9"/>
+      <c r="A259" s="12"/>
+      <c r="H259" s="13"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="H260" s="9"/>
+      <c r="A260" s="12"/>
+      <c r="H260" s="13"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="H261" s="9"/>
+      <c r="A261" s="12"/>
+      <c r="H261" s="13"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="H262" s="9"/>
+      <c r="A262" s="12"/>
+      <c r="H262" s="13"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="H263" s="9"/>
+      <c r="A263" s="12"/>
+      <c r="H263" s="13"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="H264" s="9"/>
+      <c r="A264" s="12"/>
+      <c r="H264" s="13"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="H265" s="9"/>
+      <c r="A265" s="12"/>
+      <c r="H265" s="13"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="H266" s="9"/>
+      <c r="A266" s="12"/>
+      <c r="H266" s="13"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="H267" s="9"/>
+      <c r="A267" s="12"/>
+      <c r="H267" s="13"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="H268" s="9"/>
+      <c r="A268" s="12"/>
+      <c r="H268" s="13"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="H269" s="9"/>
+      <c r="A269" s="12"/>
+      <c r="H269" s="13"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="H270" s="9"/>
+      <c r="A270" s="12"/>
+      <c r="H270" s="13"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="H271" s="9"/>
+      <c r="A271" s="12"/>
+      <c r="H271" s="13"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="H272" s="9"/>
+      <c r="A272" s="12"/>
+      <c r="H272" s="13"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="H273" s="9"/>
+      <c r="A273" s="12"/>
+      <c r="H273" s="13"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="H274" s="9"/>
+      <c r="A274" s="12"/>
+      <c r="H274" s="13"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="H275" s="9"/>
+      <c r="A275" s="12"/>
+      <c r="H275" s="13"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="H276" s="9"/>
+      <c r="A276" s="12"/>
+      <c r="H276" s="13"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="H277" s="9"/>
+      <c r="A277" s="12"/>
+      <c r="H277" s="13"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="H278" s="9"/>
+      <c r="A278" s="12"/>
+      <c r="H278" s="13"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="H279" s="9"/>
+      <c r="A279" s="12"/>
+      <c r="H279" s="13"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="H280" s="9"/>
+      <c r="A280" s="12"/>
+      <c r="H280" s="13"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="H281" s="9"/>
+      <c r="A281" s="12"/>
+      <c r="H281" s="13"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="H282" s="9"/>
+      <c r="A282" s="12"/>
+      <c r="H282" s="13"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="H283" s="9"/>
+      <c r="A283" s="12"/>
+      <c r="H283" s="13"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="H284" s="9"/>
+      <c r="A284" s="12"/>
+      <c r="H284" s="13"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="H285" s="9"/>
+      <c r="A285" s="12"/>
+      <c r="H285" s="13"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="H286" s="9"/>
+      <c r="A286" s="12"/>
+      <c r="H286" s="13"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="H287" s="9"/>
+      <c r="A287" s="12"/>
+      <c r="H287" s="13"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="H288" s="9"/>
+      <c r="A288" s="12"/>
+      <c r="H288" s="13"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="H289" s="9"/>
+      <c r="A289" s="12"/>
+      <c r="H289" s="13"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="H290" s="9"/>
+      <c r="A290" s="12"/>
+      <c r="H290" s="13"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="H291" s="9"/>
+      <c r="A291" s="12"/>
+      <c r="H291" s="13"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="H292" s="9"/>
+      <c r="A292" s="12"/>
+      <c r="H292" s="13"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="H293" s="9"/>
+      <c r="A293" s="12"/>
+      <c r="H293" s="13"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="H294" s="9"/>
+      <c r="A294" s="12"/>
+      <c r="H294" s="13"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="H295" s="9"/>
+      <c r="A295" s="12"/>
+      <c r="H295" s="13"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="H296" s="9"/>
+      <c r="A296" s="12"/>
+      <c r="H296" s="13"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="H297" s="9"/>
+      <c r="A297" s="12"/>
+      <c r="H297" s="13"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="H298" s="9"/>
+      <c r="A298" s="12"/>
+      <c r="H298" s="13"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="H299" s="9"/>
+      <c r="A299" s="12"/>
+      <c r="H299" s="13"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="H300" s="9"/>
+      <c r="A300" s="12"/>
+      <c r="H300" s="13"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="H301" s="9"/>
+      <c r="A301" s="12"/>
+      <c r="H301" s="13"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="H302" s="9"/>
+      <c r="A302" s="12"/>
+      <c r="H302" s="13"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="H303" s="9"/>
+      <c r="A303" s="12"/>
+      <c r="H303" s="13"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="H304" s="9"/>
+      <c r="A304" s="12"/>
+      <c r="H304" s="13"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="H305" s="9"/>
+      <c r="A305" s="12"/>
+      <c r="H305" s="13"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="H306" s="9"/>
+      <c r="A306" s="12"/>
+      <c r="H306" s="13"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="H307" s="9"/>
+      <c r="A307" s="12"/>
+      <c r="H307" s="13"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="H308" s="9"/>
+      <c r="A308" s="12"/>
+      <c r="H308" s="13"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="H309" s="9"/>
+      <c r="A309" s="12"/>
+      <c r="H309" s="13"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="H310" s="9"/>
+      <c r="A310" s="12"/>
+      <c r="H310" s="13"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="H311" s="9"/>
+      <c r="A311" s="12"/>
+      <c r="H311" s="13"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="H312" s="9"/>
+      <c r="A312" s="12"/>
+      <c r="H312" s="13"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="H313" s="9"/>
+      <c r="A313" s="12"/>
+      <c r="H313" s="13"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="H314" s="9"/>
+      <c r="A314" s="12"/>
+      <c r="H314" s="13"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="H315" s="9"/>
+      <c r="A315" s="12"/>
+      <c r="H315" s="13"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="H316" s="9"/>
+      <c r="A316" s="12"/>
+      <c r="H316" s="13"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="H317" s="9"/>
+      <c r="A317" s="12"/>
+      <c r="H317" s="13"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="H318" s="9"/>
+      <c r="A318" s="12"/>
+      <c r="H318" s="13"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="H319" s="9"/>
+      <c r="A319" s="12"/>
+      <c r="H319" s="13"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="H320" s="9"/>
+      <c r="A320" s="12"/>
+      <c r="H320" s="13"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="H321" s="9"/>
+      <c r="A321" s="12"/>
+      <c r="H321" s="13"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="H322" s="9"/>
+      <c r="A322" s="12"/>
+      <c r="H322" s="13"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="H323" s="9"/>
+      <c r="A323" s="12"/>
+      <c r="H323" s="13"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="H324" s="9"/>
+      <c r="A324" s="12"/>
+      <c r="H324" s="13"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="H325" s="9"/>
+      <c r="A325" s="12"/>
+      <c r="H325" s="13"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="H326" s="9"/>
+      <c r="A326" s="12"/>
+      <c r="H326" s="13"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="H327" s="9"/>
+      <c r="A327" s="12"/>
+      <c r="H327" s="13"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="H328" s="9"/>
+      <c r="A328" s="12"/>
+      <c r="H328" s="13"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="H329" s="9"/>
+      <c r="A329" s="12"/>
+      <c r="H329" s="13"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="H330" s="9"/>
+      <c r="A330" s="12"/>
+      <c r="H330" s="13"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="H331" s="9"/>
+      <c r="A331" s="12"/>
+      <c r="H331" s="13"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="H332" s="9"/>
+      <c r="A332" s="12"/>
+      <c r="H332" s="13"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="H333" s="9"/>
+      <c r="A333" s="12"/>
+      <c r="H333" s="13"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="H334" s="9"/>
+      <c r="A334" s="12"/>
+      <c r="H334" s="13"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="H335" s="9"/>
+      <c r="A335" s="12"/>
+      <c r="H335" s="13"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="H336" s="9"/>
+      <c r="A336" s="12"/>
+      <c r="H336" s="13"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="H337" s="9"/>
+      <c r="A337" s="12"/>
+      <c r="H337" s="13"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="H338" s="9"/>
+      <c r="A338" s="12"/>
+      <c r="H338" s="13"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="H339" s="9"/>
+      <c r="A339" s="12"/>
+      <c r="H339" s="13"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="H340" s="9"/>
+      <c r="A340" s="12"/>
+      <c r="H340" s="13"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="H341" s="9"/>
+      <c r="A341" s="12"/>
+      <c r="H341" s="13"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="H342" s="9"/>
+      <c r="A342" s="12"/>
+      <c r="H342" s="13"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="H343" s="9"/>
+      <c r="A343" s="12"/>
+      <c r="H343" s="13"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="H344" s="9"/>
+      <c r="A344" s="12"/>
+      <c r="H344" s="13"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="H345" s="9"/>
+      <c r="A345" s="12"/>
+      <c r="H345" s="13"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="H346" s="9"/>
+      <c r="A346" s="12"/>
+      <c r="H346" s="13"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="H347" s="9"/>
+      <c r="A347" s="12"/>
+      <c r="H347" s="13"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="H348" s="9"/>
+      <c r="A348" s="12"/>
+      <c r="H348" s="13"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="H349" s="9"/>
+      <c r="A349" s="12"/>
+      <c r="H349" s="13"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="H350" s="9"/>
+      <c r="A350" s="12"/>
+      <c r="H350" s="13"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="H351" s="9"/>
+      <c r="A351" s="12"/>
+      <c r="H351" s="13"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="H352" s="9"/>
+      <c r="A352" s="12"/>
+      <c r="H352" s="13"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="H353" s="9"/>
+      <c r="A353" s="12"/>
+      <c r="H353" s="13"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="H354" s="9"/>
+      <c r="A354" s="12"/>
+      <c r="H354" s="13"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="H355" s="9"/>
+      <c r="A355" s="12"/>
+      <c r="H355" s="13"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="H356" s="9"/>
+      <c r="A356" s="12"/>
+      <c r="H356" s="13"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="H357" s="9"/>
+      <c r="A357" s="12"/>
+      <c r="H357" s="13"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="H358" s="9"/>
+      <c r="A358" s="12"/>
+      <c r="H358" s="13"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="H359" s="9"/>
+      <c r="A359" s="12"/>
+      <c r="H359" s="13"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="H360" s="9"/>
+      <c r="A360" s="12"/>
+      <c r="H360" s="13"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="H361" s="9"/>
+      <c r="A361" s="12"/>
+      <c r="H361" s="13"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="H362" s="9"/>
+      <c r="A362" s="12"/>
+      <c r="H362" s="13"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="H363" s="9"/>
+      <c r="A363" s="12"/>
+      <c r="H363" s="13"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="H364" s="9"/>
+      <c r="A364" s="12"/>
+      <c r="H364" s="13"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="H365" s="9"/>
+      <c r="A365" s="12"/>
+      <c r="H365" s="13"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="H366" s="9"/>
+      <c r="A366" s="12"/>
+      <c r="H366" s="13"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="H367" s="9"/>
+      <c r="A367" s="12"/>
+      <c r="H367" s="13"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="H368" s="9"/>
+      <c r="A368" s="12"/>
+      <c r="H368" s="13"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="H369" s="9"/>
+      <c r="A369" s="12"/>
+      <c r="H369" s="13"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="H370" s="9"/>
+      <c r="A370" s="12"/>
+      <c r="H370" s="13"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="H371" s="9"/>
+      <c r="A371" s="12"/>
+      <c r="H371" s="13"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="H372" s="9"/>
+      <c r="A372" s="12"/>
+      <c r="H372" s="13"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="H373" s="9"/>
+      <c r="A373" s="12"/>
+      <c r="H373" s="13"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="H374" s="9"/>
+      <c r="A374" s="12"/>
+      <c r="H374" s="13"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="H375" s="9"/>
+      <c r="A375" s="12"/>
+      <c r="H375" s="13"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="H376" s="9"/>
+      <c r="A376" s="12"/>
+      <c r="H376" s="13"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="H377" s="9"/>
+      <c r="A377" s="12"/>
+      <c r="H377" s="13"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="H378" s="9"/>
+      <c r="A378" s="12"/>
+      <c r="H378" s="13"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="H379" s="9"/>
+      <c r="A379" s="12"/>
+      <c r="H379" s="13"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="H380" s="9"/>
+      <c r="A380" s="12"/>
+      <c r="H380" s="13"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="H381" s="9"/>
+      <c r="A381" s="12"/>
+      <c r="H381" s="13"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="H382" s="9"/>
+      <c r="A382" s="12"/>
+      <c r="H382" s="13"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="H383" s="9"/>
+      <c r="A383" s="12"/>
+      <c r="H383" s="13"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="H384" s="9"/>
+      <c r="A384" s="12"/>
+      <c r="H384" s="13"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="H385" s="9"/>
+      <c r="A385" s="12"/>
+      <c r="H385" s="13"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="H386" s="9"/>
+      <c r="A386" s="12"/>
+      <c r="H386" s="13"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="H387" s="9"/>
+      <c r="A387" s="12"/>
+      <c r="H387" s="13"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="H388" s="9"/>
+      <c r="A388" s="12"/>
+      <c r="H388" s="13"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="H389" s="9"/>
+      <c r="A389" s="12"/>
+      <c r="H389" s="13"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="H390" s="9"/>
+      <c r="A390" s="12"/>
+      <c r="H390" s="13"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="H391" s="9"/>
+      <c r="A391" s="12"/>
+      <c r="H391" s="13"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="H392" s="9"/>
+      <c r="A392" s="12"/>
+      <c r="H392" s="13"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="H393" s="9"/>
+      <c r="A393" s="12"/>
+      <c r="H393" s="13"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="H394" s="9"/>
+      <c r="A394" s="12"/>
+      <c r="H394" s="13"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="H395" s="9"/>
+      <c r="A395" s="12"/>
+      <c r="H395" s="13"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="H396" s="9"/>
+      <c r="A396" s="12"/>
+      <c r="H396" s="13"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="H397" s="9"/>
+      <c r="A397" s="12"/>
+      <c r="H397" s="13"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="H398" s="9"/>
+      <c r="A398" s="12"/>
+      <c r="H398" s="13"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="H399" s="9"/>
+      <c r="A399" s="12"/>
+      <c r="H399" s="13"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="H400" s="9"/>
+      <c r="A400" s="12"/>
+      <c r="H400" s="13"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="H401" s="9"/>
+      <c r="A401" s="12"/>
+      <c r="H401" s="13"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="H402" s="9"/>
+      <c r="A402" s="12"/>
+      <c r="H402" s="13"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="H403" s="9"/>
+      <c r="A403" s="12"/>
+      <c r="H403" s="13"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="H404" s="9"/>
+      <c r="A404" s="12"/>
+      <c r="H404" s="13"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="H405" s="9"/>
+      <c r="A405" s="12"/>
+      <c r="H405" s="13"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="H406" s="9"/>
+      <c r="A406" s="12"/>
+      <c r="H406" s="13"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="H407" s="9"/>
+      <c r="A407" s="12"/>
+      <c r="H407" s="13"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="H408" s="9"/>
+      <c r="A408" s="12"/>
+      <c r="H408" s="13"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="H409" s="9"/>
+      <c r="A409" s="12"/>
+      <c r="H409" s="13"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="H410" s="9"/>
+      <c r="A410" s="12"/>
+      <c r="H410" s="13"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="H411" s="9"/>
+      <c r="A411" s="12"/>
+      <c r="H411" s="13"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="H412" s="9"/>
+      <c r="A412" s="12"/>
+      <c r="H412" s="13"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="H413" s="9"/>
+      <c r="A413" s="12"/>
+      <c r="H413" s="13"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="H414" s="9"/>
+      <c r="A414" s="12"/>
+      <c r="H414" s="13"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="H415" s="9"/>
+      <c r="A415" s="12"/>
+      <c r="H415" s="13"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="H416" s="9"/>
+      <c r="A416" s="12"/>
+      <c r="H416" s="13"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="H417" s="9"/>
+      <c r="A417" s="12"/>
+      <c r="H417" s="13"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="H418" s="9"/>
+      <c r="A418" s="12"/>
+      <c r="H418" s="13"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="H419" s="9"/>
+      <c r="A419" s="12"/>
+      <c r="H419" s="13"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="H420" s="9"/>
+      <c r="A420" s="12"/>
+      <c r="H420" s="13"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="H421" s="9"/>
+      <c r="A421" s="12"/>
+      <c r="H421" s="13"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="H422" s="9"/>
+      <c r="A422" s="12"/>
+      <c r="H422" s="13"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="H423" s="9"/>
+      <c r="A423" s="12"/>
+      <c r="H423" s="13"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="H424" s="9"/>
+      <c r="A424" s="12"/>
+      <c r="H424" s="13"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="H425" s="9"/>
+      <c r="A425" s="12"/>
+      <c r="H425" s="13"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="H426" s="9"/>
+      <c r="A426" s="12"/>
+      <c r="H426" s="13"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="H427" s="9"/>
+      <c r="A427" s="12"/>
+      <c r="H427" s="13"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="H428" s="9"/>
+      <c r="A428" s="12"/>
+      <c r="H428" s="13"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="H429" s="9"/>
+      <c r="A429" s="12"/>
+      <c r="H429" s="13"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="H430" s="9"/>
+      <c r="A430" s="12"/>
+      <c r="H430" s="13"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="H431" s="9"/>
+      <c r="A431" s="12"/>
+      <c r="H431" s="13"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="H432" s="9"/>
+      <c r="A432" s="12"/>
+      <c r="H432" s="13"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="H433" s="9"/>
+      <c r="A433" s="12"/>
+      <c r="H433" s="13"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="H434" s="9"/>
+      <c r="A434" s="12"/>
+      <c r="H434" s="13"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="H435" s="9"/>
+      <c r="A435" s="12"/>
+      <c r="H435" s="13"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="H436" s="9"/>
+      <c r="A436" s="12"/>
+      <c r="H436" s="13"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="H437" s="9"/>
+      <c r="A437" s="12"/>
+      <c r="H437" s="13"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="H438" s="9"/>
+      <c r="A438" s="12"/>
+      <c r="H438" s="13"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="H439" s="9"/>
+      <c r="A439" s="12"/>
+      <c r="H439" s="13"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="H440" s="9"/>
+      <c r="A440" s="12"/>
+      <c r="H440" s="13"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="H441" s="9"/>
+      <c r="A441" s="12"/>
+      <c r="H441" s="13"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="H442" s="9"/>
+      <c r="A442" s="12"/>
+      <c r="H442" s="13"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="H443" s="9"/>
+      <c r="A443" s="12"/>
+      <c r="H443" s="13"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="H444" s="9"/>
+      <c r="A444" s="12"/>
+      <c r="H444" s="13"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="H445" s="9"/>
+      <c r="A445" s="12"/>
+      <c r="H445" s="13"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="H446" s="9"/>
+      <c r="A446" s="12"/>
+      <c r="H446" s="13"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="H447" s="9"/>
+      <c r="A447" s="12"/>
+      <c r="H447" s="13"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="H448" s="9"/>
+      <c r="A448" s="12"/>
+      <c r="H448" s="13"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="H449" s="9"/>
+      <c r="A449" s="12"/>
+      <c r="H449" s="13"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="H450" s="9"/>
+      <c r="A450" s="12"/>
+      <c r="H450" s="13"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="H451" s="9"/>
+      <c r="A451" s="12"/>
+      <c r="H451" s="13"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="H452" s="9"/>
+      <c r="A452" s="12"/>
+      <c r="H452" s="13"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="H453" s="9"/>
+      <c r="A453" s="12"/>
+      <c r="H453" s="13"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="H454" s="9"/>
+      <c r="A454" s="12"/>
+      <c r="H454" s="13"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="H455" s="9"/>
+      <c r="A455" s="12"/>
+      <c r="H455" s="13"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="H456" s="9"/>
+      <c r="A456" s="12"/>
+      <c r="H456" s="13"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="H457" s="9"/>
+      <c r="A457" s="12"/>
+      <c r="H457" s="13"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="H458" s="9"/>
+      <c r="A458" s="12"/>
+      <c r="H458" s="13"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="H459" s="9"/>
+      <c r="A459" s="12"/>
+      <c r="H459" s="13"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="H460" s="9"/>
+      <c r="A460" s="12"/>
+      <c r="H460" s="13"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="H461" s="9"/>
+      <c r="A461" s="12"/>
+      <c r="H461" s="13"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="H462" s="9"/>
+      <c r="A462" s="12"/>
+      <c r="H462" s="13"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="H463" s="9"/>
+      <c r="A463" s="12"/>
+      <c r="H463" s="13"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="H464" s="9"/>
+      <c r="A464" s="12"/>
+      <c r="H464" s="13"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="H465" s="9"/>
+      <c r="A465" s="12"/>
+      <c r="H465" s="13"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="H466" s="9"/>
+      <c r="A466" s="12"/>
+      <c r="H466" s="13"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="H467" s="9"/>
+      <c r="A467" s="12"/>
+      <c r="H467" s="13"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="H468" s="9"/>
+      <c r="A468" s="12"/>
+      <c r="H468" s="13"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="H469" s="9"/>
+      <c r="A469" s="12"/>
+      <c r="H469" s="13"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="H470" s="9"/>
+      <c r="A470" s="12"/>
+      <c r="H470" s="13"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="H471" s="9"/>
+      <c r="A471" s="12"/>
+      <c r="H471" s="13"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="H472" s="9"/>
+      <c r="A472" s="12"/>
+      <c r="H472" s="13"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="H473" s="9"/>
+      <c r="A473" s="12"/>
+      <c r="H473" s="13"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="H474" s="9"/>
+      <c r="A474" s="12"/>
+      <c r="H474" s="13"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="H475" s="9"/>
+      <c r="A475" s="12"/>
+      <c r="H475" s="13"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="H476" s="9"/>
+      <c r="A476" s="12"/>
+      <c r="H476" s="13"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="H477" s="9"/>
+      <c r="A477" s="12"/>
+      <c r="H477" s="13"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="H478" s="9"/>
+      <c r="A478" s="12"/>
+      <c r="H478" s="13"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="H479" s="9"/>
+      <c r="A479" s="12"/>
+      <c r="H479" s="13"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="H480" s="9"/>
+      <c r="A480" s="12"/>
+      <c r="H480" s="13"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="H481" s="9"/>
+      <c r="A481" s="12"/>
+      <c r="H481" s="13"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="H482" s="9"/>
+      <c r="A482" s="12"/>
+      <c r="H482" s="13"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="H483" s="9"/>
+      <c r="A483" s="12"/>
+      <c r="H483" s="13"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="H484" s="9"/>
+      <c r="A484" s="12"/>
+      <c r="H484" s="13"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="H485" s="9"/>
+      <c r="A485" s="12"/>
+      <c r="H485" s="13"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="H486" s="9"/>
+      <c r="A486" s="12"/>
+      <c r="H486" s="13"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="H487" s="9"/>
+      <c r="A487" s="12"/>
+      <c r="H487" s="13"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="H488" s="9"/>
+      <c r="A488" s="12"/>
+      <c r="H488" s="13"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="H489" s="9"/>
+      <c r="A489" s="12"/>
+      <c r="H489" s="13"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="H490" s="9"/>
+      <c r="A490" s="12"/>
+      <c r="H490" s="13"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="H491" s="9"/>
+      <c r="A491" s="12"/>
+      <c r="H491" s="13"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="H492" s="9"/>
+      <c r="A492" s="12"/>
+      <c r="H492" s="13"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="H493" s="9"/>
+      <c r="A493" s="12"/>
+      <c r="H493" s="13"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="H494" s="9"/>
+      <c r="A494" s="12"/>
+      <c r="H494" s="13"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="H495" s="9"/>
+      <c r="A495" s="12"/>
+      <c r="H495" s="13"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="H496" s="9"/>
+      <c r="A496" s="12"/>
+      <c r="H496" s="13"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="H497" s="9"/>
+      <c r="A497" s="12"/>
+      <c r="H497" s="13"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="H498" s="9"/>
+      <c r="A498" s="12"/>
+      <c r="H498" s="13"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="H499" s="9"/>
+      <c r="A499" s="12"/>
+      <c r="H499" s="13"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="H500" s="9"/>
+      <c r="A500" s="12"/>
+      <c r="H500" s="13"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="H501" s="9"/>
+      <c r="A501" s="12"/>
+      <c r="H501" s="13"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="H502" s="9"/>
+      <c r="A502" s="12"/>
+      <c r="H502" s="13"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="H503" s="9"/>
+      <c r="A503" s="12"/>
+      <c r="H503" s="13"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="H504" s="9"/>
+      <c r="A504" s="12"/>
+      <c r="H504" s="13"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="H505" s="9"/>
+      <c r="A505" s="12"/>
+      <c r="H505" s="13"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="H506" s="9"/>
+      <c r="A506" s="12"/>
+      <c r="H506" s="13"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="H507" s="9"/>
+      <c r="A507" s="12"/>
+      <c r="H507" s="13"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="H508" s="9"/>
+      <c r="A508" s="12"/>
+      <c r="H508" s="13"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="H509" s="9"/>
+      <c r="A509" s="12"/>
+      <c r="H509" s="13"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="H510" s="9"/>
+      <c r="A510" s="12"/>
+      <c r="H510" s="13"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="H511" s="9"/>
+      <c r="A511" s="12"/>
+      <c r="H511" s="13"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="H512" s="9"/>
+      <c r="A512" s="12"/>
+      <c r="H512" s="13"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="H513" s="9"/>
+      <c r="A513" s="12"/>
+      <c r="H513" s="13"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="H514" s="9"/>
+      <c r="A514" s="12"/>
+      <c r="H514" s="13"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="H515" s="9"/>
+      <c r="A515" s="12"/>
+      <c r="H515" s="13"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="H516" s="9"/>
+      <c r="A516" s="12"/>
+      <c r="H516" s="13"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="H517" s="9"/>
+      <c r="A517" s="12"/>
+      <c r="H517" s="13"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="H518" s="9"/>
+      <c r="A518" s="12"/>
+      <c r="H518" s="13"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="H519" s="9"/>
+      <c r="A519" s="12"/>
+      <c r="H519" s="13"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="H520" s="9"/>
+      <c r="A520" s="12"/>
+      <c r="H520" s="13"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="H521" s="9"/>
+      <c r="A521" s="12"/>
+      <c r="H521" s="13"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="H522" s="9"/>
+      <c r="A522" s="12"/>
+      <c r="H522" s="13"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="H523" s="9"/>
+      <c r="A523" s="12"/>
+      <c r="H523" s="13"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="H524" s="9"/>
+      <c r="A524" s="12"/>
+      <c r="H524" s="13"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="H525" s="9"/>
+      <c r="A525" s="12"/>
+      <c r="H525" s="13"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="H526" s="9"/>
+      <c r="A526" s="12"/>
+      <c r="H526" s="13"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="H527" s="9"/>
+      <c r="A527" s="12"/>
+      <c r="H527" s="13"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="H528" s="9"/>
+      <c r="A528" s="12"/>
+      <c r="H528" s="13"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="H529" s="9"/>
+      <c r="A529" s="12"/>
+      <c r="H529" s="13"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="H530" s="9"/>
+      <c r="A530" s="12"/>
+      <c r="H530" s="13"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="H531" s="9"/>
+      <c r="A531" s="12"/>
+      <c r="H531" s="13"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="H532" s="9"/>
+      <c r="A532" s="12"/>
+      <c r="H532" s="13"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="H533" s="9"/>
+      <c r="A533" s="12"/>
+      <c r="H533" s="13"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="H534" s="9"/>
+      <c r="A534" s="12"/>
+      <c r="H534" s="13"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="H535" s="9"/>
+      <c r="A535" s="12"/>
+      <c r="H535" s="13"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="H536" s="9"/>
+      <c r="A536" s="12"/>
+      <c r="H536" s="13"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="H537" s="9"/>
+      <c r="A537" s="12"/>
+      <c r="H537" s="13"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="H538" s="9"/>
+      <c r="A538" s="12"/>
+      <c r="H538" s="13"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="H539" s="9"/>
+      <c r="A539" s="12"/>
+      <c r="H539" s="13"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="H540" s="9"/>
+      <c r="A540" s="12"/>
+      <c r="H540" s="13"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="H541" s="9"/>
+      <c r="A541" s="12"/>
+      <c r="H541" s="13"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="H542" s="9"/>
+      <c r="A542" s="12"/>
+      <c r="H542" s="13"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="H543" s="9"/>
+      <c r="A543" s="12"/>
+      <c r="H543" s="13"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="H544" s="9"/>
+      <c r="A544" s="12"/>
+      <c r="H544" s="13"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="H545" s="9"/>
+      <c r="A545" s="12"/>
+      <c r="H545" s="13"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="H546" s="9"/>
+      <c r="A546" s="12"/>
+      <c r="H546" s="13"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="H547" s="9"/>
+      <c r="A547" s="12"/>
+      <c r="H547" s="13"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="H548" s="9"/>
+      <c r="A548" s="12"/>
+      <c r="H548" s="13"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="H549" s="9"/>
+      <c r="A549" s="12"/>
+      <c r="H549" s="13"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="H550" s="9"/>
+      <c r="A550" s="12"/>
+      <c r="H550" s="13"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="H551" s="9"/>
+      <c r="A551" s="12"/>
+      <c r="H551" s="13"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="H552" s="9"/>
+      <c r="A552" s="12"/>
+      <c r="H552" s="13"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="H553" s="9"/>
+      <c r="A553" s="12"/>
+      <c r="H553" s="13"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="H554" s="9"/>
+      <c r="A554" s="12"/>
+      <c r="H554" s="13"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="H555" s="9"/>
+      <c r="A555" s="12"/>
+      <c r="H555" s="13"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="H556" s="9"/>
+      <c r="A556" s="12"/>
+      <c r="H556" s="13"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="H557" s="9"/>
+      <c r="A557" s="12"/>
+      <c r="H557" s="13"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="H558" s="9"/>
+      <c r="A558" s="12"/>
+      <c r="H558" s="13"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="H559" s="9"/>
+      <c r="A559" s="12"/>
+      <c r="H559" s="13"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="H560" s="9"/>
+      <c r="A560" s="12"/>
+      <c r="H560" s="13"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="H561" s="9"/>
+      <c r="A561" s="12"/>
+      <c r="H561" s="13"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="H562" s="9"/>
+      <c r="A562" s="12"/>
+      <c r="H562" s="13"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="H563" s="9"/>
+      <c r="A563" s="12"/>
+      <c r="H563" s="13"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="H564" s="9"/>
+      <c r="A564" s="12"/>
+      <c r="H564" s="13"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="H565" s="9"/>
+      <c r="A565" s="12"/>
+      <c r="H565" s="13"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="H566" s="9"/>
+      <c r="A566" s="12"/>
+      <c r="H566" s="13"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="H567" s="9"/>
+      <c r="A567" s="12"/>
+      <c r="H567" s="13"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="H568" s="9"/>
+      <c r="A568" s="12"/>
+      <c r="H568" s="13"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="H569" s="9"/>
+      <c r="A569" s="12"/>
+      <c r="H569" s="13"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="H570" s="9"/>
+      <c r="A570" s="12"/>
+      <c r="H570" s="13"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="H571" s="9"/>
+      <c r="A571" s="12"/>
+      <c r="H571" s="13"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="H572" s="9"/>
+      <c r="A572" s="12"/>
+      <c r="H572" s="13"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="H573" s="9"/>
+      <c r="A573" s="12"/>
+      <c r="H573" s="13"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="H574" s="9"/>
+      <c r="A574" s="12"/>
+      <c r="H574" s="13"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="H575" s="9"/>
+      <c r="A575" s="12"/>
+      <c r="H575" s="13"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="H576" s="9"/>
+      <c r="A576" s="12"/>
+      <c r="H576" s="13"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="H577" s="9"/>
+      <c r="A577" s="12"/>
+      <c r="H577" s="13"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="H578" s="9"/>
+      <c r="A578" s="12"/>
+      <c r="H578" s="13"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="H579" s="9"/>
+      <c r="A579" s="12"/>
+      <c r="H579" s="13"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="H580" s="9"/>
+      <c r="A580" s="12"/>
+      <c r="H580" s="13"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="H581" s="9"/>
+      <c r="A581" s="12"/>
+      <c r="H581" s="13"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="H582" s="9"/>
+      <c r="A582" s="12"/>
+      <c r="H582" s="13"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="H583" s="9"/>
+      <c r="A583" s="12"/>
+      <c r="H583" s="13"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="H584" s="9"/>
+      <c r="A584" s="12"/>
+      <c r="H584" s="13"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="H585" s="9"/>
+      <c r="A585" s="12"/>
+      <c r="H585" s="13"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="H586" s="9"/>
+      <c r="A586" s="12"/>
+      <c r="H586" s="13"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="H587" s="9"/>
+      <c r="A587" s="12"/>
+      <c r="H587" s="13"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="H588" s="9"/>
+      <c r="A588" s="12"/>
+      <c r="H588" s="13"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="H589" s="9"/>
+      <c r="A589" s="12"/>
+      <c r="H589" s="13"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="H590" s="9"/>
+      <c r="A590" s="12"/>
+      <c r="H590" s="13"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="H591" s="9"/>
+      <c r="A591" s="12"/>
+      <c r="H591" s="13"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="H592" s="9"/>
+      <c r="A592" s="12"/>
+      <c r="H592" s="13"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="H593" s="9"/>
+      <c r="A593" s="12"/>
+      <c r="H593" s="13"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="H594" s="9"/>
+      <c r="A594" s="12"/>
+      <c r="H594" s="13"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="H595" s="9"/>
+      <c r="A595" s="12"/>
+      <c r="H595" s="13"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="H596" s="9"/>
+      <c r="A596" s="12"/>
+      <c r="H596" s="13"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="H597" s="9"/>
+      <c r="A597" s="12"/>
+      <c r="H597" s="13"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="H598" s="9"/>
+      <c r="A598" s="12"/>
+      <c r="H598" s="13"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="H599" s="9"/>
+      <c r="A599" s="12"/>
+      <c r="H599" s="13"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="H600" s="9"/>
+      <c r="A600" s="12"/>
+      <c r="H600" s="13"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="H601" s="9"/>
+      <c r="A601" s="12"/>
+      <c r="H601" s="13"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="H602" s="9"/>
+      <c r="A602" s="12"/>
+      <c r="H602" s="13"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="H603" s="9"/>
+      <c r="A603" s="12"/>
+      <c r="H603" s="13"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="H604" s="9"/>
+      <c r="A604" s="12"/>
+      <c r="H604" s="13"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="H605" s="9"/>
+      <c r="A605" s="12"/>
+      <c r="H605" s="13"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="H606" s="9"/>
+      <c r="A606" s="12"/>
+      <c r="H606" s="13"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="H607" s="9"/>
+      <c r="A607" s="12"/>
+      <c r="H607" s="13"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="H608" s="9"/>
+      <c r="A608" s="12"/>
+      <c r="H608" s="13"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="H609" s="9"/>
+      <c r="A609" s="12"/>
+      <c r="H609" s="13"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="H610" s="9"/>
+      <c r="A610" s="12"/>
+      <c r="H610" s="13"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="H611" s="9"/>
+      <c r="A611" s="12"/>
+      <c r="H611" s="13"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="H612" s="9"/>
+      <c r="A612" s="12"/>
+      <c r="H612" s="13"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="H613" s="9"/>
+      <c r="A613" s="12"/>
+      <c r="H613" s="13"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="H614" s="9"/>
+      <c r="A614" s="12"/>
+      <c r="H614" s="13"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="H615" s="9"/>
+      <c r="A615" s="12"/>
+      <c r="H615" s="13"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="H616" s="9"/>
+      <c r="A616" s="12"/>
+      <c r="H616" s="13"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="H617" s="9"/>
+      <c r="A617" s="12"/>
+      <c r="H617" s="13"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="H618" s="9"/>
+      <c r="A618" s="12"/>
+      <c r="H618" s="13"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="H619" s="9"/>
+      <c r="A619" s="12"/>
+      <c r="H619" s="13"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="H620" s="9"/>
+      <c r="A620" s="12"/>
+      <c r="H620" s="13"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="H621" s="9"/>
+      <c r="A621" s="12"/>
+      <c r="H621" s="13"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="H622" s="9"/>
+      <c r="A622" s="12"/>
+      <c r="H622" s="13"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="H623" s="9"/>
+      <c r="A623" s="12"/>
+      <c r="H623" s="13"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="H624" s="9"/>
+      <c r="A624" s="12"/>
+      <c r="H624" s="13"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="H625" s="9"/>
+      <c r="A625" s="12"/>
+      <c r="H625" s="13"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="H626" s="9"/>
+      <c r="A626" s="12"/>
+      <c r="H626" s="13"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="H627" s="9"/>
+      <c r="A627" s="12"/>
+      <c r="H627" s="13"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="H628" s="9"/>
+      <c r="A628" s="12"/>
+      <c r="H628" s="13"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="H629" s="9"/>
+      <c r="A629" s="12"/>
+      <c r="H629" s="13"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="H630" s="9"/>
+      <c r="A630" s="12"/>
+      <c r="H630" s="13"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="H631" s="9"/>
+      <c r="A631" s="12"/>
+      <c r="H631" s="13"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="H632" s="9"/>
+      <c r="A632" s="12"/>
+      <c r="H632" s="13"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="H633" s="9"/>
+      <c r="A633" s="12"/>
+      <c r="H633" s="13"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="H634" s="9"/>
+      <c r="A634" s="12"/>
+      <c r="H634" s="13"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="H635" s="9"/>
+      <c r="A635" s="12"/>
+      <c r="H635" s="13"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="H636" s="9"/>
+      <c r="A636" s="12"/>
+      <c r="H636" s="13"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="H637" s="9"/>
+      <c r="A637" s="12"/>
+      <c r="H637" s="13"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="H638" s="9"/>
+      <c r="A638" s="12"/>
+      <c r="H638" s="13"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="H639" s="9"/>
+      <c r="A639" s="12"/>
+      <c r="H639" s="13"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="H640" s="9"/>
+      <c r="A640" s="12"/>
+      <c r="H640" s="13"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="H641" s="9"/>
+      <c r="A641" s="12"/>
+      <c r="H641" s="13"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="H642" s="9"/>
+      <c r="A642" s="12"/>
+      <c r="H642" s="13"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="H643" s="9"/>
+      <c r="A643" s="12"/>
+      <c r="H643" s="13"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="H644" s="9"/>
+      <c r="A644" s="12"/>
+      <c r="H644" s="13"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="H645" s="9"/>
+      <c r="A645" s="12"/>
+      <c r="H645" s="13"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="H646" s="9"/>
+      <c r="A646" s="12"/>
+      <c r="H646" s="13"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="H647" s="9"/>
+      <c r="A647" s="12"/>
+      <c r="H647" s="13"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="H648" s="9"/>
+      <c r="A648" s="12"/>
+      <c r="H648" s="13"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="H649" s="9"/>
+      <c r="A649" s="12"/>
+      <c r="H649" s="13"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="H650" s="9"/>
+      <c r="A650" s="12"/>
+      <c r="H650" s="13"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="H651" s="9"/>
+      <c r="A651" s="12"/>
+      <c r="H651" s="13"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="H652" s="9"/>
+      <c r="A652" s="12"/>
+      <c r="H652" s="13"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="H653" s="9"/>
+      <c r="A653" s="12"/>
+      <c r="H653" s="13"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="H654" s="9"/>
+      <c r="A654" s="12"/>
+      <c r="H654" s="13"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="H655" s="9"/>
+      <c r="A655" s="12"/>
+      <c r="H655" s="13"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="H656" s="9"/>
+      <c r="A656" s="12"/>
+      <c r="H656" s="13"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="H657" s="9"/>
+      <c r="A657" s="12"/>
+      <c r="H657" s="13"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="H658" s="9"/>
+      <c r="A658" s="12"/>
+      <c r="H658" s="13"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="H659" s="9"/>
+      <c r="A659" s="12"/>
+      <c r="H659" s="13"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="H660" s="9"/>
+      <c r="A660" s="12"/>
+      <c r="H660" s="13"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="H661" s="9"/>
+      <c r="A661" s="12"/>
+      <c r="H661" s="13"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="H662" s="9"/>
+      <c r="A662" s="12"/>
+      <c r="H662" s="13"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="H663" s="9"/>
+      <c r="A663" s="12"/>
+      <c r="H663" s="13"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="H664" s="9"/>
+      <c r="A664" s="12"/>
+      <c r="H664" s="13"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="H665" s="9"/>
+      <c r="A665" s="12"/>
+      <c r="H665" s="13"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="H666" s="9"/>
+      <c r="A666" s="12"/>
+      <c r="H666" s="13"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="H667" s="9"/>
+      <c r="A667" s="12"/>
+      <c r="H667" s="13"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="H668" s="9"/>
+      <c r="A668" s="12"/>
+      <c r="H668" s="13"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="H669" s="9"/>
+      <c r="A669" s="12"/>
+      <c r="H669" s="13"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="H670" s="9"/>
+      <c r="A670" s="12"/>
+      <c r="H670" s="13"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="H671" s="9"/>
+      <c r="A671" s="12"/>
+      <c r="H671" s="13"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="H672" s="9"/>
+      <c r="A672" s="12"/>
+      <c r="H672" s="13"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="H673" s="9"/>
+      <c r="A673" s="12"/>
+      <c r="H673" s="13"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="H674" s="9"/>
+      <c r="A674" s="12"/>
+      <c r="H674" s="13"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="H675" s="9"/>
+      <c r="A675" s="12"/>
+      <c r="H675" s="13"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="H676" s="9"/>
+      <c r="A676" s="12"/>
+      <c r="H676" s="13"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="H677" s="9"/>
+      <c r="A677" s="12"/>
+      <c r="H677" s="13"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="H678" s="9"/>
+      <c r="A678" s="12"/>
+      <c r="H678" s="13"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="H679" s="9"/>
+      <c r="A679" s="12"/>
+      <c r="H679" s="13"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="H680" s="9"/>
+      <c r="A680" s="12"/>
+      <c r="H680" s="13"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="H681" s="9"/>
+      <c r="A681" s="12"/>
+      <c r="H681" s="13"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="H682" s="9"/>
+      <c r="A682" s="12"/>
+      <c r="H682" s="13"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="H683" s="9"/>
+      <c r="A683" s="12"/>
+      <c r="H683" s="13"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="H684" s="9"/>
+      <c r="A684" s="12"/>
+      <c r="H684" s="13"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="H685" s="9"/>
+      <c r="A685" s="12"/>
+      <c r="H685" s="13"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="H686" s="9"/>
+      <c r="A686" s="12"/>
+      <c r="H686" s="13"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="H687" s="9"/>
+      <c r="A687" s="12"/>
+      <c r="H687" s="13"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="H688" s="9"/>
+      <c r="A688" s="12"/>
+      <c r="H688" s="13"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="H689" s="9"/>
+      <c r="A689" s="12"/>
+      <c r="H689" s="13"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="H690" s="9"/>
+      <c r="A690" s="12"/>
+      <c r="H690" s="13"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="H691" s="9"/>
+      <c r="A691" s="12"/>
+      <c r="H691" s="13"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="H692" s="9"/>
+      <c r="A692" s="12"/>
+      <c r="H692" s="13"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="H693" s="9"/>
+      <c r="A693" s="12"/>
+      <c r="H693" s="13"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="H694" s="9"/>
+      <c r="A694" s="12"/>
+      <c r="H694" s="13"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="H695" s="9"/>
+      <c r="A695" s="12"/>
+      <c r="H695" s="13"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="H696" s="9"/>
+      <c r="A696" s="12"/>
+      <c r="H696" s="13"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="H697" s="9"/>
+      <c r="A697" s="12"/>
+      <c r="H697" s="13"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="H698" s="9"/>
+      <c r="A698" s="12"/>
+      <c r="H698" s="13"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="H699" s="9"/>
+      <c r="A699" s="12"/>
+      <c r="H699" s="13"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="H700" s="9"/>
+      <c r="A700" s="12"/>
+      <c r="H700" s="13"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="H701" s="9"/>
+      <c r="A701" s="12"/>
+      <c r="H701" s="13"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="H702" s="9"/>
+      <c r="A702" s="12"/>
+      <c r="H702" s="13"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="H703" s="9"/>
+      <c r="A703" s="12"/>
+      <c r="H703" s="13"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="H704" s="9"/>
+      <c r="A704" s="12"/>
+      <c r="H704" s="13"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="H705" s="9"/>
+      <c r="A705" s="12"/>
+      <c r="H705" s="13"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="H706" s="9"/>
+      <c r="A706" s="12"/>
+      <c r="H706" s="13"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="H707" s="9"/>
+      <c r="A707" s="12"/>
+      <c r="H707" s="13"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="H708" s="9"/>
+      <c r="A708" s="12"/>
+      <c r="H708" s="13"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="H709" s="9"/>
+      <c r="A709" s="12"/>
+      <c r="H709" s="13"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="H710" s="9"/>
+      <c r="A710" s="12"/>
+      <c r="H710" s="13"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="H711" s="9"/>
+      <c r="A711" s="12"/>
+      <c r="H711" s="13"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="H712" s="9"/>
+      <c r="A712" s="12"/>
+      <c r="H712" s="13"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="H713" s="9"/>
+      <c r="A713" s="12"/>
+      <c r="H713" s="13"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="H714" s="9"/>
+      <c r="A714" s="12"/>
+      <c r="H714" s="13"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="H715" s="9"/>
+      <c r="A715" s="12"/>
+      <c r="H715" s="13"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="H716" s="9"/>
+      <c r="A716" s="12"/>
+      <c r="H716" s="13"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="H717" s="9"/>
+      <c r="A717" s="12"/>
+      <c r="H717" s="13"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="H718" s="9"/>
+      <c r="A718" s="12"/>
+      <c r="H718" s="13"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="H719" s="9"/>
+      <c r="A719" s="12"/>
+      <c r="H719" s="13"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="H720" s="9"/>
+      <c r="A720" s="12"/>
+      <c r="H720" s="13"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="H721" s="9"/>
+      <c r="A721" s="12"/>
+      <c r="H721" s="13"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="H722" s="9"/>
+      <c r="A722" s="12"/>
+      <c r="H722" s="13"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="H723" s="9"/>
+      <c r="A723" s="12"/>
+      <c r="H723" s="13"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="H724" s="9"/>
+      <c r="A724" s="12"/>
+      <c r="H724" s="13"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="H725" s="9"/>
+      <c r="A725" s="12"/>
+      <c r="H725" s="13"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="H726" s="9"/>
+      <c r="A726" s="12"/>
+      <c r="H726" s="13"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="H727" s="9"/>
+      <c r="A727" s="12"/>
+      <c r="H727" s="13"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="H728" s="9"/>
+      <c r="A728" s="12"/>
+      <c r="H728" s="13"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="H729" s="9"/>
+      <c r="A729" s="12"/>
+      <c r="H729" s="13"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="H730" s="9"/>
+      <c r="A730" s="12"/>
+      <c r="H730" s="13"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="H731" s="9"/>
+      <c r="A731" s="12"/>
+      <c r="H731" s="13"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="H732" s="9"/>
+      <c r="A732" s="12"/>
+      <c r="H732" s="13"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="H733" s="9"/>
+      <c r="A733" s="12"/>
+      <c r="H733" s="13"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="H734" s="9"/>
+      <c r="A734" s="12"/>
+      <c r="H734" s="13"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="H735" s="9"/>
+      <c r="A735" s="12"/>
+      <c r="H735" s="13"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="H736" s="9"/>
+      <c r="A736" s="12"/>
+      <c r="H736" s="13"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="H737" s="9"/>
+      <c r="A737" s="12"/>
+      <c r="H737" s="13"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="H738" s="9"/>
+      <c r="A738" s="12"/>
+      <c r="H738" s="13"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="H739" s="9"/>
+      <c r="A739" s="12"/>
+      <c r="H739" s="13"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="H740" s="9"/>
+      <c r="A740" s="12"/>
+      <c r="H740" s="13"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="H741" s="9"/>
+      <c r="A741" s="12"/>
+      <c r="H741" s="13"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="H742" s="9"/>
+      <c r="A742" s="12"/>
+      <c r="H742" s="13"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="H743" s="9"/>
+      <c r="A743" s="12"/>
+      <c r="H743" s="13"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="H744" s="9"/>
+      <c r="A744" s="12"/>
+      <c r="H744" s="13"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="H745" s="9"/>
+      <c r="A745" s="12"/>
+      <c r="H745" s="13"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="H746" s="9"/>
+      <c r="A746" s="12"/>
+      <c r="H746" s="13"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="H747" s="9"/>
+      <c r="A747" s="12"/>
+      <c r="H747" s="13"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="H748" s="9"/>
+      <c r="A748" s="12"/>
+      <c r="H748" s="13"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="H749" s="9"/>
+      <c r="A749" s="12"/>
+      <c r="H749" s="13"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="H750" s="9"/>
+      <c r="A750" s="12"/>
+      <c r="H750" s="13"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="H751" s="9"/>
+      <c r="A751" s="12"/>
+      <c r="H751" s="13"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="H752" s="9"/>
+      <c r="A752" s="12"/>
+      <c r="H752" s="13"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="H753" s="9"/>
+      <c r="A753" s="12"/>
+      <c r="H753" s="13"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="H754" s="9"/>
+      <c r="A754" s="12"/>
+      <c r="H754" s="13"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="H755" s="9"/>
+      <c r="A755" s="12"/>
+      <c r="H755" s="13"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="H756" s="9"/>
+      <c r="A756" s="12"/>
+      <c r="H756" s="13"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="H757" s="9"/>
+      <c r="A757" s="12"/>
+      <c r="H757" s="13"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="H758" s="9"/>
+      <c r="A758" s="12"/>
+      <c r="H758" s="13"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="H759" s="9"/>
+      <c r="A759" s="12"/>
+      <c r="H759" s="13"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="H760" s="9"/>
+      <c r="A760" s="12"/>
+      <c r="H760" s="13"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="H761" s="9"/>
+      <c r="A761" s="12"/>
+      <c r="H761" s="13"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="H762" s="9"/>
+      <c r="A762" s="12"/>
+      <c r="H762" s="13"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="H763" s="9"/>
+      <c r="A763" s="12"/>
+      <c r="H763" s="13"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="H764" s="9"/>
+      <c r="A764" s="12"/>
+      <c r="H764" s="13"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="H765" s="9"/>
+      <c r="A765" s="12"/>
+      <c r="H765" s="13"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="H766" s="9"/>
+      <c r="A766" s="12"/>
+      <c r="H766" s="13"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="H767" s="9"/>
+      <c r="A767" s="12"/>
+      <c r="H767" s="13"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="H768" s="9"/>
+      <c r="A768" s="12"/>
+      <c r="H768" s="13"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="H769" s="9"/>
+      <c r="A769" s="12"/>
+      <c r="H769" s="13"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="H770" s="9"/>
+      <c r="A770" s="12"/>
+      <c r="H770" s="13"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="H771" s="9"/>
+      <c r="A771" s="12"/>
+      <c r="H771" s="13"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="H772" s="9"/>
+      <c r="A772" s="12"/>
+      <c r="H772" s="13"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="H773" s="9"/>
+      <c r="A773" s="12"/>
+      <c r="H773" s="13"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="H774" s="9"/>
+      <c r="A774" s="12"/>
+      <c r="H774" s="13"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="H775" s="9"/>
+      <c r="A775" s="12"/>
+      <c r="H775" s="13"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="H776" s="9"/>
+      <c r="A776" s="12"/>
+      <c r="H776" s="13"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="H777" s="9"/>
+      <c r="A777" s="12"/>
+      <c r="H777" s="13"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="H778" s="9"/>
+      <c r="A778" s="12"/>
+      <c r="H778" s="13"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="H779" s="9"/>
+      <c r="A779" s="12"/>
+      <c r="H779" s="13"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="H780" s="9"/>
+      <c r="A780" s="12"/>
+      <c r="H780" s="13"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="H781" s="9"/>
+      <c r="A781" s="12"/>
+      <c r="H781" s="13"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="H782" s="9"/>
+      <c r="A782" s="12"/>
+      <c r="H782" s="13"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="H783" s="9"/>
+      <c r="A783" s="12"/>
+      <c r="H783" s="13"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="H784" s="9"/>
+      <c r="A784" s="12"/>
+      <c r="H784" s="13"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="H785" s="9"/>
+      <c r="A785" s="12"/>
+      <c r="H785" s="13"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="H786" s="9"/>
+      <c r="A786" s="12"/>
+      <c r="H786" s="13"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="H787" s="9"/>
+      <c r="A787" s="12"/>
+      <c r="H787" s="13"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="H788" s="9"/>
+      <c r="A788" s="12"/>
+      <c r="H788" s="13"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="H789" s="9"/>
+      <c r="A789" s="12"/>
+      <c r="H789" s="13"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="H790" s="9"/>
+      <c r="A790" s="12"/>
+      <c r="H790" s="13"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="H791" s="9"/>
+      <c r="A791" s="12"/>
+      <c r="H791" s="13"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="H792" s="9"/>
+      <c r="A792" s="12"/>
+      <c r="H792" s="13"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="H793" s="9"/>
+      <c r="A793" s="12"/>
+      <c r="H793" s="13"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="H794" s="9"/>
+      <c r="A794" s="12"/>
+      <c r="H794" s="13"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="H795" s="9"/>
+      <c r="A795" s="12"/>
+      <c r="H795" s="13"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="H796" s="9"/>
+      <c r="A796" s="12"/>
+      <c r="H796" s="13"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="H797" s="9"/>
+      <c r="A797" s="12"/>
+      <c r="H797" s="13"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="H798" s="9"/>
+      <c r="A798" s="12"/>
+      <c r="H798" s="13"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="H799" s="9"/>
+      <c r="A799" s="12"/>
+      <c r="H799" s="13"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="H800" s="9"/>
+      <c r="A800" s="12"/>
+      <c r="H800" s="13"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="H801" s="9"/>
+      <c r="A801" s="12"/>
+      <c r="H801" s="13"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="H802" s="9"/>
+      <c r="A802" s="12"/>
+      <c r="H802" s="13"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="H803" s="9"/>
+      <c r="A803" s="12"/>
+      <c r="H803" s="13"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="H804" s="9"/>
+      <c r="A804" s="12"/>
+      <c r="H804" s="13"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="H805" s="9"/>
+      <c r="A805" s="12"/>
+      <c r="H805" s="13"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="H806" s="9"/>
+      <c r="A806" s="12"/>
+      <c r="H806" s="13"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="H807" s="9"/>
+      <c r="A807" s="12"/>
+      <c r="H807" s="13"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="H808" s="9"/>
+      <c r="A808" s="12"/>
+      <c r="H808" s="13"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="H809" s="9"/>
+      <c r="A809" s="12"/>
+      <c r="H809" s="13"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="H810" s="9"/>
+      <c r="A810" s="12"/>
+      <c r="H810" s="13"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="H811" s="9"/>
+      <c r="A811" s="12"/>
+      <c r="H811" s="13"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="H812" s="9"/>
+      <c r="A812" s="12"/>
+      <c r="H812" s="13"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="H813" s="9"/>
+      <c r="A813" s="12"/>
+      <c r="H813" s="13"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="H814" s="9"/>
+      <c r="A814" s="12"/>
+      <c r="H814" s="13"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="H815" s="9"/>
+      <c r="A815" s="12"/>
+      <c r="H815" s="13"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="H816" s="9"/>
+      <c r="A816" s="12"/>
+      <c r="H816" s="13"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="H817" s="9"/>
+      <c r="A817" s="12"/>
+      <c r="H817" s="13"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="H818" s="9"/>
+      <c r="A818" s="12"/>
+      <c r="H818" s="13"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="H819" s="9"/>
+      <c r="A819" s="12"/>
+      <c r="H819" s="13"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="H820" s="9"/>
+      <c r="A820" s="12"/>
+      <c r="H820" s="13"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="H821" s="9"/>
+      <c r="A821" s="12"/>
+      <c r="H821" s="13"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="H822" s="9"/>
+      <c r="A822" s="12"/>
+      <c r="H822" s="13"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="H823" s="9"/>
+      <c r="A823" s="12"/>
+      <c r="H823" s="13"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="H824" s="9"/>
+      <c r="A824" s="12"/>
+      <c r="H824" s="13"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="H825" s="9"/>
+      <c r="A825" s="12"/>
+      <c r="H825" s="13"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="H826" s="9"/>
+      <c r="A826" s="12"/>
+      <c r="H826" s="13"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="H827" s="9"/>
+      <c r="A827" s="12"/>
+      <c r="H827" s="13"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="H828" s="9"/>
+      <c r="A828" s="12"/>
+      <c r="H828" s="13"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="H829" s="9"/>
+      <c r="A829" s="12"/>
+      <c r="H829" s="13"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="H830" s="9"/>
+      <c r="A830" s="12"/>
+      <c r="H830" s="13"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="H831" s="9"/>
+      <c r="A831" s="12"/>
+      <c r="H831" s="13"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="H832" s="9"/>
+      <c r="A832" s="12"/>
+      <c r="H832" s="13"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="H833" s="9"/>
+      <c r="A833" s="12"/>
+      <c r="H833" s="13"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="H834" s="9"/>
+      <c r="A834" s="12"/>
+      <c r="H834" s="13"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="H835" s="9"/>
+      <c r="A835" s="12"/>
+      <c r="H835" s="13"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="H836" s="9"/>
+      <c r="A836" s="12"/>
+      <c r="H836" s="13"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="H837" s="9"/>
+      <c r="A837" s="12"/>
+      <c r="H837" s="13"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="H838" s="9"/>
+      <c r="A838" s="12"/>
+      <c r="H838" s="13"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="H839" s="9"/>
+      <c r="A839" s="12"/>
+      <c r="H839" s="13"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="H840" s="9"/>
+      <c r="A840" s="12"/>
+      <c r="H840" s="13"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="H841" s="9"/>
+      <c r="A841" s="12"/>
+      <c r="H841" s="13"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="H842" s="9"/>
+      <c r="A842" s="12"/>
+      <c r="H842" s="13"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="H843" s="9"/>
+      <c r="A843" s="12"/>
+      <c r="H843" s="13"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="H844" s="9"/>
+      <c r="A844" s="12"/>
+      <c r="H844" s="13"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="H845" s="9"/>
+      <c r="A845" s="12"/>
+      <c r="H845" s="13"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="H846" s="9"/>
+      <c r="A846" s="12"/>
+      <c r="H846" s="13"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="H847" s="9"/>
+      <c r="A847" s="12"/>
+      <c r="H847" s="13"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="H848" s="9"/>
+      <c r="A848" s="12"/>
+      <c r="H848" s="13"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="H849" s="9"/>
+      <c r="A849" s="12"/>
+      <c r="H849" s="13"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="H850" s="9"/>
+      <c r="A850" s="12"/>
+      <c r="H850" s="13"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="H851" s="9"/>
+      <c r="A851" s="12"/>
+      <c r="H851" s="13"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="H852" s="9"/>
+      <c r="A852" s="12"/>
+      <c r="H852" s="13"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="H853" s="9"/>
+      <c r="A853" s="12"/>
+      <c r="H853" s="13"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="H854" s="9"/>
+      <c r="A854" s="12"/>
+      <c r="H854" s="13"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="H855" s="9"/>
+      <c r="A855" s="12"/>
+      <c r="H855" s="13"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="H856" s="9"/>
+      <c r="A856" s="12"/>
+      <c r="H856" s="13"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="H857" s="9"/>
+      <c r="A857" s="12"/>
+      <c r="H857" s="13"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="H858" s="9"/>
+      <c r="A858" s="12"/>
+      <c r="H858" s="13"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="H859" s="9"/>
+      <c r="A859" s="12"/>
+      <c r="H859" s="13"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="H860" s="9"/>
+      <c r="A860" s="12"/>
+      <c r="H860" s="13"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="H861" s="9"/>
+      <c r="A861" s="12"/>
+      <c r="H861" s="13"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="H862" s="9"/>
+      <c r="A862" s="12"/>
+      <c r="H862" s="13"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="H863" s="9"/>
+      <c r="A863" s="12"/>
+      <c r="H863" s="13"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="H864" s="9"/>
+      <c r="A864" s="12"/>
+      <c r="H864" s="13"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="H865" s="9"/>
+      <c r="A865" s="12"/>
+      <c r="H865" s="13"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="H866" s="9"/>
+      <c r="A866" s="12"/>
+      <c r="H866" s="13"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="H867" s="9"/>
+      <c r="A867" s="12"/>
+      <c r="H867" s="13"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="H868" s="9"/>
+      <c r="A868" s="12"/>
+      <c r="H868" s="13"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="H869" s="9"/>
+      <c r="A869" s="12"/>
+      <c r="H869" s="13"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="H870" s="9"/>
+      <c r="A870" s="12"/>
+      <c r="H870" s="13"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="H871" s="9"/>
+      <c r="A871" s="12"/>
+      <c r="H871" s="13"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="H872" s="9"/>
+      <c r="A872" s="12"/>
+      <c r="H872" s="13"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="H873" s="9"/>
+      <c r="A873" s="12"/>
+      <c r="H873" s="13"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="H874" s="9"/>
+      <c r="A874" s="12"/>
+      <c r="H874" s="13"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="H875" s="9"/>
+      <c r="A875" s="12"/>
+      <c r="H875" s="13"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="H876" s="9"/>
+      <c r="A876" s="12"/>
+      <c r="H876" s="13"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="H877" s="9"/>
+      <c r="A877" s="12"/>
+      <c r="H877" s="13"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="H878" s="9"/>
+      <c r="A878" s="12"/>
+      <c r="H878" s="13"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="H879" s="9"/>
+      <c r="A879" s="12"/>
+      <c r="H879" s="13"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="H880" s="9"/>
+      <c r="A880" s="12"/>
+      <c r="H880" s="13"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="H881" s="9"/>
+      <c r="A881" s="12"/>
+      <c r="H881" s="13"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="H882" s="9"/>
+      <c r="A882" s="12"/>
+      <c r="H882" s="13"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="H883" s="9"/>
+      <c r="A883" s="12"/>
+      <c r="H883" s="13"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="H884" s="9"/>
+      <c r="A884" s="12"/>
+      <c r="H884" s="13"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="H885" s="9"/>
+      <c r="A885" s="12"/>
+      <c r="H885" s="13"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="H886" s="9"/>
+      <c r="A886" s="12"/>
+      <c r="H886" s="13"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="H887" s="9"/>
+      <c r="A887" s="12"/>
+      <c r="H887" s="13"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="H888" s="9"/>
+      <c r="A888" s="12"/>
+      <c r="H888" s="13"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="H889" s="9"/>
+      <c r="A889" s="12"/>
+      <c r="H889" s="13"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="H890" s="9"/>
+      <c r="A890" s="12"/>
+      <c r="H890" s="13"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="H891" s="9"/>
+      <c r="A891" s="12"/>
+      <c r="H891" s="13"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="H892" s="9"/>
+      <c r="A892" s="12"/>
+      <c r="H892" s="13"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="H893" s="9"/>
+      <c r="A893" s="12"/>
+      <c r="H893" s="13"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="H894" s="9"/>
+      <c r="A894" s="12"/>
+      <c r="H894" s="13"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="H895" s="9"/>
+      <c r="A895" s="12"/>
+      <c r="H895" s="13"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="H896" s="9"/>
+      <c r="A896" s="12"/>
+      <c r="H896" s="13"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="H897" s="9"/>
+      <c r="A897" s="12"/>
+      <c r="H897" s="13"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="H898" s="9"/>
+      <c r="A898" s="12"/>
+      <c r="H898" s="13"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="H899" s="9"/>
+      <c r="A899" s="12"/>
+      <c r="H899" s="13"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="H900" s="9"/>
+      <c r="A900" s="12"/>
+      <c r="H900" s="13"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="H901" s="9"/>
+      <c r="A901" s="12"/>
+      <c r="H901" s="13"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="H902" s="9"/>
+      <c r="A902" s="12"/>
+      <c r="H902" s="13"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="H903" s="9"/>
+      <c r="A903" s="12"/>
+      <c r="H903" s="13"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="H904" s="9"/>
+      <c r="A904" s="12"/>
+      <c r="H904" s="13"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="H905" s="9"/>
+      <c r="A905" s="12"/>
+      <c r="H905" s="13"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="H906" s="9"/>
+      <c r="A906" s="12"/>
+      <c r="H906" s="13"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="H907" s="9"/>
+      <c r="A907" s="12"/>
+      <c r="H907" s="13"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="H908" s="9"/>
+      <c r="A908" s="12"/>
+      <c r="H908" s="13"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="H909" s="9"/>
+      <c r="A909" s="12"/>
+      <c r="H909" s="13"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="H910" s="9"/>
+      <c r="A910" s="12"/>
+      <c r="H910" s="13"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="H911" s="9"/>
+      <c r="A911" s="12"/>
+      <c r="H911" s="13"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="H912" s="9"/>
+      <c r="A912" s="12"/>
+      <c r="H912" s="13"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="H913" s="9"/>
+      <c r="A913" s="12"/>
+      <c r="H913" s="13"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="H914" s="9"/>
+      <c r="A914" s="12"/>
+      <c r="H914" s="13"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="H915" s="9"/>
+      <c r="A915" s="12"/>
+      <c r="H915" s="13"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="H916" s="9"/>
+      <c r="A916" s="12"/>
+      <c r="H916" s="13"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="H917" s="9"/>
+      <c r="A917" s="12"/>
+      <c r="H917" s="13"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="H918" s="9"/>
+      <c r="A918" s="12"/>
+      <c r="H918" s="13"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="H919" s="9"/>
+      <c r="A919" s="12"/>
+      <c r="H919" s="13"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="H920" s="9"/>
+      <c r="A920" s="12"/>
+      <c r="H920" s="13"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="H921" s="9"/>
+      <c r="A921" s="12"/>
+      <c r="H921" s="13"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="H922" s="9"/>
+      <c r="A922" s="12"/>
+      <c r="H922" s="13"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="H923" s="9"/>
+      <c r="A923" s="12"/>
+      <c r="H923" s="13"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="H924" s="9"/>
+      <c r="A924" s="12"/>
+      <c r="H924" s="13"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="H925" s="9"/>
+      <c r="A925" s="12"/>
+      <c r="H925" s="13"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="H926" s="9"/>
+      <c r="A926" s="12"/>
+      <c r="H926" s="13"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="H927" s="9"/>
+      <c r="A927" s="12"/>
+      <c r="H927" s="13"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="H928" s="9"/>
+      <c r="A928" s="12"/>
+      <c r="H928" s="13"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="H929" s="9"/>
+      <c r="A929" s="12"/>
+      <c r="H929" s="13"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="H930" s="9"/>
+      <c r="A930" s="12"/>
+      <c r="H930" s="13"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="H931" s="9"/>
+      <c r="A931" s="12"/>
+      <c r="H931" s="13"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="H932" s="9"/>
+      <c r="A932" s="12"/>
+      <c r="H932" s="13"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="H933" s="9"/>
+      <c r="A933" s="12"/>
+      <c r="H933" s="13"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="H934" s="9"/>
+      <c r="A934" s="12"/>
+      <c r="H934" s="13"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="H935" s="9"/>
+      <c r="A935" s="12"/>
+      <c r="H935" s="13"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="H936" s="9"/>
+      <c r="A936" s="12"/>
+      <c r="H936" s="13"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="H937" s="9"/>
+      <c r="A937" s="12"/>
+      <c r="H937" s="13"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="H938" s="9"/>
+      <c r="A938" s="12"/>
+      <c r="H938" s="13"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="H939" s="9"/>
+      <c r="A939" s="12"/>
+      <c r="H939" s="13"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="H940" s="9"/>
+      <c r="A940" s="12"/>
+      <c r="H940" s="13"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="H941" s="9"/>
+      <c r="A941" s="12"/>
+      <c r="H941" s="13"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="H942" s="9"/>
+      <c r="A942" s="12"/>
+      <c r="H942" s="13"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="H943" s="9"/>
+      <c r="A943" s="12"/>
+      <c r="H943" s="13"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="H944" s="9"/>
+      <c r="A944" s="12"/>
+      <c r="H944" s="13"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="H945" s="9"/>
+      <c r="A945" s="12"/>
+      <c r="H945" s="13"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="H946" s="9"/>
+      <c r="A946" s="12"/>
+      <c r="H946" s="13"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="H947" s="9"/>
+      <c r="A947" s="12"/>
+      <c r="H947" s="13"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="H948" s="9"/>
+      <c r="A948" s="12"/>
+      <c r="H948" s="13"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="H949" s="9"/>
+      <c r="A949" s="12"/>
+      <c r="H949" s="13"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="H950" s="9"/>
+      <c r="A950" s="12"/>
+      <c r="H950" s="13"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="H951" s="9"/>
+      <c r="A951" s="12"/>
+      <c r="H951" s="13"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="H952" s="9"/>
+      <c r="A952" s="12"/>
+      <c r="H952" s="13"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="H953" s="9"/>
+      <c r="A953" s="12"/>
+      <c r="H953" s="13"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="H954" s="9"/>
+      <c r="A954" s="12"/>
+      <c r="H954" s="13"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="H955" s="9"/>
+      <c r="A955" s="12"/>
+      <c r="H955" s="13"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="H956" s="9"/>
+      <c r="A956" s="12"/>
+      <c r="H956" s="13"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="H957" s="9"/>
+      <c r="A957" s="12"/>
+      <c r="H957" s="13"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="H958" s="9"/>
+      <c r="A958" s="12"/>
+      <c r="H958" s="13"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="H959" s="9"/>
+      <c r="A959" s="12"/>
+      <c r="H959" s="13"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="H960" s="9"/>
+      <c r="A960" s="12"/>
+      <c r="H960" s="13"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="H961" s="9"/>
+      <c r="A961" s="12"/>
+      <c r="H961" s="13"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="H962" s="9"/>
+      <c r="A962" s="12"/>
+      <c r="H962" s="13"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="H963" s="9"/>
+      <c r="A963" s="12"/>
+      <c r="H963" s="13"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="H964" s="9"/>
+      <c r="A964" s="12"/>
+      <c r="H964" s="13"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="H965" s="9"/>
+      <c r="A965" s="12"/>
+      <c r="H965" s="13"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="H966" s="9"/>
+      <c r="A966" s="12"/>
+      <c r="H966" s="13"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="H967" s="9"/>
+      <c r="A967" s="12"/>
+      <c r="H967" s="13"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="H968" s="9"/>
+      <c r="A968" s="12"/>
+      <c r="H968" s="13"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="H969" s="9"/>
+      <c r="A969" s="12"/>
+      <c r="H969" s="13"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="H970" s="9"/>
+      <c r="A970" s="12"/>
+      <c r="H970" s="13"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="H971" s="9"/>
+      <c r="A971" s="12"/>
+      <c r="H971" s="13"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="H972" s="9"/>
+      <c r="A972" s="12"/>
+      <c r="H972" s="13"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="H973" s="9"/>
+      <c r="A973" s="12"/>
+      <c r="H973" s="13"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="H974" s="9"/>
+      <c r="A974" s="12"/>
+      <c r="H974" s="13"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="H975" s="9"/>
+      <c r="A975" s="12"/>
+      <c r="H975" s="13"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="H976" s="9"/>
+      <c r="A976" s="12"/>
+      <c r="H976" s="13"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="H977" s="9"/>
+      <c r="A977" s="12"/>
+      <c r="H977" s="13"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="H978" s="9"/>
+      <c r="A978" s="12"/>
+      <c r="H978" s="13"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="H979" s="9"/>
+      <c r="A979" s="12"/>
+      <c r="H979" s="13"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="H980" s="9"/>
+      <c r="A980" s="12"/>
+      <c r="H980" s="13"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="H981" s="9"/>
+      <c r="A981" s="12"/>
+      <c r="H981" s="13"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="H982" s="9"/>
+      <c r="A982" s="12"/>
+      <c r="H982" s="13"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="H983" s="9"/>
+      <c r="A983" s="12"/>
+      <c r="H983" s="13"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="H984" s="9"/>
+      <c r="A984" s="12"/>
+      <c r="H984" s="13"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="H985" s="9"/>
+      <c r="A985" s="12"/>
+      <c r="H985" s="13"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="H986" s="9"/>
+      <c r="A986" s="12"/>
+      <c r="H986" s="13"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="H987" s="9"/>
+      <c r="A987" s="12"/>
+      <c r="H987" s="13"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="H988" s="9"/>
+      <c r="A988" s="12"/>
+      <c r="H988" s="13"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="H989" s="9"/>
+      <c r="A989" s="12"/>
+      <c r="H989" s="13"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="H990" s="9"/>
+      <c r="A990" s="12"/>
+      <c r="H990" s="13"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="H991" s="9"/>
+      <c r="A991" s="12"/>
+      <c r="H991" s="13"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="H992" s="9"/>
+      <c r="A992" s="12"/>
+      <c r="H992" s="13"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="H993" s="9"/>
+      <c r="A993" s="12"/>
+      <c r="H993" s="13"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="H994" s="9"/>
+      <c r="A994" s="12"/>
+      <c r="H994" s="13"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="H995" s="9"/>
+      <c r="A995" s="12"/>
+      <c r="H995" s="13"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="H996" s="9"/>
+      <c r="A996" s="12"/>
+      <c r="H996" s="13"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="H997" s="9"/>
+      <c r="A997" s="12"/>
+      <c r="H997" s="13"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="H998" s="9"/>
+      <c r="A998" s="12"/>
+      <c r="H998" s="13"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="H999" s="9"/>
+      <c r="A999" s="12"/>
+      <c r="H999" s="13"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="H1000" s="9"/>
+      <c r="A1000" s="12"/>
+      <c r="H1000" s="13"/>
     </row>
     <row r="1001" ht="15.75" customHeight="1">
-      <c r="H1001" s="9"/>
+      <c r="A1001" s="12"/>
+      <c r="H1001" s="13"/>
     </row>
     <row r="1002" ht="15.75" customHeight="1">
-      <c r="H1002" s="9"/>
+      <c r="A1002" s="12"/>
+      <c r="H1002" s="13"/>
     </row>
     <row r="1003" ht="15.75" customHeight="1">
-      <c r="H1003" s="9"/>
+      <c r="A1003" s="12"/>
+      <c r="H1003" s="13"/>
     </row>
     <row r="1004" ht="15.75" customHeight="1">
-      <c r="H1004" s="9"/>
+      <c r="A1004" s="12"/>
+      <c r="H1004" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
